--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -165,9 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,7 +772,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>569.8</v>
+        <v>62.8</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>33.5</v>
@@ -789,7 +780,7 @@
       <c r="E4" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -797,13 +788,13 @@
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -812,13 +803,13 @@
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>4.3</v>
@@ -826,23 +817,23 @@
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>10.3</v>
+      <c r="W4" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>12.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -857,22 +848,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>856143513.2</v>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
         <v>21.7</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+        <v>2.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -886,10 +883,10 @@
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15.5</v>
+        <v>35.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>21.6</v>
+        <v>0.4</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -898,19 +895,19 @@
         <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.7</v>
+        <v>31.2</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>41</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.2</v>
@@ -922,10 +919,10 @@
         <v>8.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>201.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.1</v>
+        <v>80.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,18 +937,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>856143513.2</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>33.9</v>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>32.1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="8" t="n">
-        <v>31.9</v>
+      <c r="F6" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -960,25 +963,25 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>12.2</v>
+      <c r="L6" s="8" t="n">
+        <v>488.7</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -987,7 +990,7 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>14.4</v>
@@ -999,10 +1002,10 @@
         <v>28.9</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>16.3</v>
@@ -1024,22 +1027,22 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>583.6</v>
+        <v>53.6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>23.1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1048,7 +1051,7 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
@@ -1057,16 +1060,16 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
+        <v>39.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>13.8</v>
@@ -1087,10 +1090,10 @@
         <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.3</v>
@@ -1109,39 +1112,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>22.7</v>
+        <v>25.1</v>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>22.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>110.8</v>
+        <v>2.2</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>36.5</v>
+        <v>0.8</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1153,7 +1154,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1162,13 +1163,13 @@
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>22.1</v>
@@ -1190,19 +1191,27 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="F9" s="10" t="n"/>
+        <v>2656.2</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>111.4</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="n">
         <v>44.2</v>
       </c>
@@ -1210,48 +1219,48 @@
         <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n">
-        <v>28.8</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183.8</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>165</v>
+        <v>1685</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>71.8</v>
+        <v>24.8</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.1</v>
+        <v>24.1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>38.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>106.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1267,15 +1276,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>534.4</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>22.3</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1288,24 +1297,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>13.7</v>
+        <v>2.7</v>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="n">
-        <v>13.4</v>
+      <c r="L10" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.2</v>
+        <v>32.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>36.6</v>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
@@ -1313,28 +1320,28 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>13.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>38.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>17.8</v>
+        <v>0.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>184.1</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>150.2</v>
+        <v>11.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1350,25 +1357,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E11" s="11" t="n">
+        <v>422.9</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>42.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
+        <v>41.1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
@@ -1380,14 +1387,18 @@
       <c r="M11" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>0.2</v>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+8
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
@@ -1397,22 +1408,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>81</v>
+        <v>31.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>47</v>
+        <v>424</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1428,29 +1439,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 6
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 317
-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>19.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.1</v>
@@ -1459,7 +1464,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1468,7 +1473,7 @@
         <v>6.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
@@ -1476,35 +1481,37 @@
       <c r="P12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="8" t="n">
-        <v>10.8</v>
+      <c r="Q12" s="3" t="n">
+        <v>31.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>29.2</v>
+        <v>92.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+76
+</t>
+        </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1520,13 +1527,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>601.3</v>
+        <v>61.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>15.4</v>
+      <c r="E13" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>24.9</v>
@@ -1534,7 +1541,7 @@
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1553,19 +1560,19 @@
         <v>12.7</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.3</v>
+      <c r="R13" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1574,19 +1581,19 @@
         <v>13.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>28.7</v>
+        <v>49.6</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>87.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1608,8 +1615,8 @@
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>17.9</v>
+      <c r="E14" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
@@ -1617,7 +1624,7 @@
       <c r="G14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1627,43 +1634,43 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>1.8</v>
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>49.5</v>
+        <v>9.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="R14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>27</v>
+        <v>41.2</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>9.199999999999999</v>
@@ -1692,12 +1699,12 @@
         <v>34.3</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G15" s="8" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1710,16 +1717,16 @@
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>48</v>
@@ -1730,11 +1737,11 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <v>14.3</v>
+      <c r="R15" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>15.4</v>
@@ -1743,7 +1750,7 @@
         <v>38</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>14</v>
@@ -1755,7 +1762,7 @@
         <v>23.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1771,16 +1778,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9572.1</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1189.6</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>82.09999999999999</v>
+        <v>2577.7</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>8.1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1789,29 +1796,39 @@
         <v>10.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>11.7</v>
+        <v>5.4</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811
+14
+</t>
+        </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>822.3</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>2121.5</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>54.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>23.6</v>
@@ -1820,23 +1837,29 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
+        <v>820.6</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="n">
         <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>148.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>11.5</v>
+        <v>19.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1852,74 +1875,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>23.6</v>
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>2.6</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61.8</v>
+        <v>6.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>30.9</v>
+      <c r="P17" s="8" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>60.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>7.3</v>
+        <v>72.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>96.3</v>
+        <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.1</v>
+        <v>212.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,63 +1957,62 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>552.1</v>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+2
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 7
-</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n"/>
+        <v>34.9</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F18" s="9" t="n"/>
       <c r="G18" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>1.1</v>
+        <v>32.9</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>37.6</v>
+        <v>166.9</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
@@ -2005,7 +2027,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2020,13 +2042,19 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>326.4</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E19" s="13" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+2975
+</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
       </c>
@@ -2034,7 +2062,7 @@
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.8</v>
@@ -2043,7 +2071,7 @@
         <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>13.5</v>
@@ -2051,19 +2079,17 @@
       <c r="M19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R19" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2073,19 +2099,19 @@
         <v>12.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>20.4</v>
+        <v>4.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2101,15 +2127,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D20" s="13" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.3</v>
+        <v>12.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2118,34 +2149,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32</v>
+        <v>28.3</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2154,15 +2185,17 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41.4</v>
+        <v>4.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="X20" s="3" t="n"/>
+      <c r="X20" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="Y20" s="3" t="n">
         <v>32</v>
       </c>
@@ -2181,59 +2214,61 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="12" t="n">
-        <v>1.4</v>
+        <v>542.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1.1</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>25.6</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>492</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>28.3</v>
+        <v>30.7</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>2.6</v>
+        <v>12.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>26.3</v>
@@ -2248,7 +2283,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2264,16 +2299,16 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>516.3</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>3.6</v>
+        <v>536.3</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>34.1</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>22.5</v>
+      <c r="F22" s="11" t="n">
+        <v>43.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>16.6</v>
@@ -2282,31 +2317,31 @@
         <v>13.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J22" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>51</v>
+        <v>21.1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>30.7</v>
+        <v>22.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>4.5</v>
@@ -2315,19 +2350,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
+        <v>14.9</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>98.2</v>
+        <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2346,63 +2381,67 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>117.1</v>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="10" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>17.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>11.6</v>
+        <v>86.8</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44255
+82947
+</t>
+        </is>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="K23" s="3" t="n"/>
+        <v>7.2</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.7</v>
+        <v>1.1</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>23</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>44.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>31.3</v>
+        <v>5.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>7.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>29</v>
+        <v>292</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.5</v>
+        <v>30.5</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>68.8</v>
@@ -2411,9 +2450,11 @@
         <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>192.1</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2428,51 +2469,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5032.1</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>5026.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>17.4</v>
+      <c r="E24" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>78.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>50.3</v>
+        <v>5.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R24" s="8" t="n">
+      <c r="Q24" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2485,7 +2526,7 @@
         <v>87.2</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
@@ -2494,10 +2535,10 @@
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2513,68 +2554,77 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G25" s="8" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
+        <v>400.8</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>14.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n">
-        <v>88.8</v>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+2
+</t>
+        </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>45.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2593,39 +2643,41 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>44.8</v>
+      <c r="E26" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n">
-        <v>10.9</v>
+        <v>72.3</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2637,25 +2689,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="U26" s="8" t="n">
-        <v>2823.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>4.8</v>
+      <c r="U26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2672,30 +2724,32 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
+        <v>5.1</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E27" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>82</v>
+      <c r="F27" s="11" t="n">
+        <v>28.58</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>681.6</v>
-      </c>
-      <c r="J27" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2703,13 +2757,13 @@
         <v>10.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>98.5</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1322</v>
+        <v>528</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>82.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>29.3</v>
@@ -2718,28 +2772,32 @@
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>28.2</v>
+        <v>3.4</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>44.3</v>
+        <v>4.2</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>264.4</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>20.8</v>
+        <v>26.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2757,74 +2815,78 @@
       <c r="C28" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>33.2</v>
+      <c r="D28" s="3" t="n">
+        <v>33.4</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>23.5</v>
+      <c r="F28" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J28" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>47</v>
+        <v>428</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>22.5</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>7.2</v>
+        <v>13.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>20.8</v>
+        <v>126.5</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2840,13 +2902,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
+        <v>0.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>14.6</v>
+        <v>3.4</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>4.6</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>23.9</v>
@@ -2855,16 +2917,16 @@
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2873,10 +2935,10 @@
         <v>10.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>41.3</v>
+        <v>4.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2884,16 +2946,18 @@
       <c r="Q29" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>9.4</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>43.4</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>27.7</v>
       </c>
@@ -2921,73 +2985,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>624.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>1561.6</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>29.3</v>
+      <c r="F30" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>81.8</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.9</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>83.5</v>
+        <v>33.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>66.8</v>
+        <v>6.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42</v>
+        <v>42.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>18.6</v>
+        <v>28.3</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -3004,31 +3068,31 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F31" s="9" t="n">
+      <c r="E31" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>18</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>522.4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>18.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3042,21 +3106,19 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>14.2</v>
+      <c r="P31" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
@@ -3070,7 +3132,7 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3088,36 +3150,32 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>11.4</v>
-      </c>
+        <v>23.2</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.8</v>
@@ -3135,27 +3193,27 @@
         <v>4.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="T32" s="3" t="n"/>
+        <v>4.7</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>42.4</v>
+        <v>424.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>1.5</v>
+        <v>28.5</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>24.6</v>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3169,14 +3227,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>10.6</v>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="11" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1.6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>22.2</v>
@@ -3185,58 +3241,58 @@
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15.8</v>
+        <v>35.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141.8</v>
+        <v>4.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>10.2</v>
+      <c r="R33" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>6.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
+        <v>44.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3256,7 +3312,7 @@
         <v>386.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>14.5</v>
@@ -3271,7 +3327,7 @@
         <v>1.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3280,10 +3336,10 @@
         <v>6</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>41.2</v>
+        <v>17.2</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.8</v>
@@ -3295,13 +3351,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>2.1</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>30.3</v>
@@ -3316,13 +3372,17 @@
         <v>12.7</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>5</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+178
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3338,13 +3398,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>437.9</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>85.59999999999999</v>
+        <v>433.9</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>23.2</v>
@@ -3353,13 +3413,13 @@
         <v>15.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>19.1</v>
+        <v>12.4</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>14.2</v>
@@ -3368,14 +3428,16 @@
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N35" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>2.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>19</v>
@@ -3387,26 +3449,24 @@
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>10.8</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3421,10 +3481,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>222.2</v>
+        <v>22.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25.5</v>
+        <v>30.3</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>17</v>
@@ -3432,7 +3492,7 @@
       <c r="F36" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3442,10 +3502,10 @@
         <v>4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>44.2</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
@@ -3453,14 +3513,12 @@
       <c r="M36" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>19.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>30.8</v>
@@ -3469,25 +3527,25 @@
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.2</v>
+        <v>21.6</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3503,57 +3561,53 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>222.2</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>18.8</v>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>18.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>111.2</v>
+        <v>1.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>11.2</v>
+        <v>42.4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>821.9</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>240.2</v>
+        <v>20.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>389.8</v>
+        <v>59.8</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>4.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>124.9</v>
+        <v>34.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>3.4</v>
@@ -3562,15 +3616,17 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>183.1</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>96.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3587,26 +3643,26 @@
       <c r="C38" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="10" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="F38" s="9" t="n">
-        <v>10.3</v>
+      <c r="F38" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>55.8</v>
+        <v>5.8</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>301</v>
+      <c r="J38" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>36.1</v>
@@ -3615,43 +3671,43 @@
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>13.2</v>
+        <v>53.2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>4.7</v>
+        <v>47.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>14.5</v>
+        <v>33.5</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>48.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>151</v>
+        <v>11.6</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3670,39 +3726,41 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.1</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F39" s="12" t="n">
+        <v>5444.4</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>12.1</v>
+        <v>6.5</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>6000.4</v>
+      <c r="M39" s="3" t="n">
+        <v>40.6</v>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3717,25 +3775,25 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>20.3</v>
+        <v>0.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>29.4</v>
+        <v>2.4</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W39" s="8" t="n">
-        <v>15</v>
+      <c r="W39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3751,10 +3809,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
+        <v>6.4</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>30.3</v>
+        <v>29.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>14.2</v>
@@ -3766,28 +3824,26 @@
         <v>15</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>51.2</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="K40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.4</v>
+        <v>94.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3795,14 +3851,14 @@
       <c r="Q40" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="R40" s="8" t="n">
-        <v>15</v>
+      <c r="R40" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>822.4</v>
+        <v>22.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>34.2</v>
@@ -3814,13 +3870,13 @@
         <v>14.7</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3836,76 +3892,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>25.5</v>
+        <v>6.4</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>34.8</v>
+        <v>30.3</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>22.7</v>
+      <c r="F41" s="11" t="n">
+        <v>2.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>11.2</v>
+        <v>16.8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>9.5</v>
+        <v>23.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>52</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>19.5</v>
+        <v>197.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>32.6</v>
+        <v>2.6</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>828.9</v>
+        <v>28.9</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>223.6</v>
+        <v>16.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3920,14 +3976,18 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>25.5</v>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+4811
+</t>
+        </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>46.2</v>
+        <v>31.4</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>23.8</v>
@@ -3935,62 +3995,62 @@
       <c r="G42" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>53</v>
+      <c r="H42" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>18.3</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+      <c r="K42" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>11.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.1</v>
+        <v>45.5</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>165.5</v>
+        <v>16.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4006,76 +4066,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>324</v>
+        <v>23.9</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>9.5</v>
+        <v>98.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>58</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>76.2</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="n">
-        <v>4.2</v>
+        <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>24.6</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>45.1</v>
+        <v>19.9</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>25.3</v>
+        <v>285.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.8</v>
+        <v>16.5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4091,76 +4149,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>30.7</v>
+        <v>23.9</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>60.5</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G44" s="8" t="n">
-        <v>14.9</v>
+      <c r="G44" s="3" t="n">
+        <v>4.4</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>19.7</v>
+        <v>5.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.4</v>
+        <v>581.5</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>7.8</v>
+      <c r="R44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>89.8</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>1.4</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>12.9</v>
+        <v>8.4</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4176,76 +4234,78 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>231.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>185.7</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="F45" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
         <v>22.9</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.9</v>
+        <v>119.1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>356</v>
+        <v>6.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9</v>
+        <v>90.8</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>181.1</v>
+        <v>16.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>119.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>0.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>18.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>91.2</v>
+        <v>22.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>881.8</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>19.2</v>
+        <v>2.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>72.2</v>
+        <v>52.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>75.2</v>
+        <v>21.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>186.5</v>
+        <v>14.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>184.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>19.6</v>
+        <v>2.2</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+11
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4261,70 +4321,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>139.9</v>
+        <v>232.2</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>232.1</v>
       </c>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>35</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
+        <v>524.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>26.5</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>92</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>332.1</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>30.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>24.8</v>
+        <v>751.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>14.4</v>
+        <v>18.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>10.8</v>
+        <v>64.8</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>19.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -59,8 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -772,69 +772,57 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>62.8</v>
+        <v>1569.8</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F4" s="12" t="n">
+      <c r="E4" s="11" t="inlineStr"/>
+      <c r="F4" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n">
-        <v>2.8</v>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>13.2</v>
+      <c r="Q4" s="8" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -848,33 +836,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>512.7</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="E5" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>2.8</v>
+      <c r="G5" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>12.9</v>
+        <v>44.2</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.8</v>
@@ -882,47 +866,45 @@
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>35.5</v>
+      <c r="M5" s="8" t="n">
+        <v>65.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R5" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>14.2</v>
+        <v>5.7</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="8" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>10.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>8.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>21.2</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>80.8</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -937,24 +919,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>1504.8</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>32.1</v>
+        <v>34.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="G6" s="8" t="n">
+        <v>20623.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -963,55 +941,53 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>488.7</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>8.4</v>
+        <v>16</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>89.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>42.4</v>
+        <v>1</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16.3</v>
+        <v>201.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>3.3</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,76 +1003,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>53.6</v>
+        <v>583.6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F7" s="12" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I7" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>46.1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>54.6</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="n">
-        <v>25</v>
+        <v>22.1</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>51.7</v>
+        <v>4.4</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>28.9</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>12.2</v>
+        <v>116.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.3</v>
+        <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,37 +1086,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+        <v>485.1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>91</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>26.5</v>
+        <v>236.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1150,32 +1124,32 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>7.9</v>
+      <c r="S8" s="8" t="n">
+        <v>71</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="U8" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U8" s="8" t="n">
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>1.7</v>
+        <v>45.1</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>22.1</v>
+        <v>86.7</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>34.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1191,76 +1165,72 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2656.2</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>111.4</v>
-      </c>
+        <v>2636</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1169.7</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2262
-411464141
-</t>
-        </is>
+        <v>116.4</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.2</v>
+        <v>1644.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M9" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>2.8</v>
+        <v>258.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>949.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1685</v>
+        <v>1169</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S9" s="3" t="n"/>
+        <v>71.8</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>127.7</v>
+      </c>
       <c r="T9" s="3" t="n">
-        <v>55.9</v>
+        <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.1</v>
+        <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>139.7</v>
+        <v>1139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.6</v>
+        <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>38.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>16.2</v>
+        <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>90.2</v>
+        <v>1120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1276,72 +1246,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F10" s="12" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>3.4</v>
+        <v>13.7</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>32.6</v>
+        <v>16.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="P10" s="3" t="n"/>
+        <v>236.6</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>99.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U10" s="8" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
-        <v>2.9</v>
+      <c r="V10" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>38.2</v>
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0.8</v>
+        <v>17.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>184.1</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>11.2</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1357,75 +1329,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>422.9</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>42.1</v>
+        <v>1427.8</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.1</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q11" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="8" t="n">
+        <v>148.9</v>
+      </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>424</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1440,78 +1400,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>21.7</v>
+        <v>206.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>28.7</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.2</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>31.3</v>
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6.8</v>
+        <v>16.2</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>92.2</v>
+        <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-76
-</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1527,75 +1483,75 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>61.3</v>
+        <v>1601.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E13" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>11.8</v>
+      <c r="H13" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>11.7</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>1249</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>33.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>87.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>28.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>15.1</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>7.1</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>1265.4</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1610,22 +1566,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
+        <v>1488</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F14" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>11.4</v>
+      <c r="H14" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>8.1</v>
@@ -1634,51 +1590,45 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P14" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>4.4</v>
+        <v>161.1</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>431.2</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1693,76 +1643,68 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.4</v>
+        <v>1832.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="E15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G15" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3.6</v>
+        <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.8</v>
+        <v>92.8</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>22.1</v>
-      </c>
+        <v>115.4</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
       <c r="W15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>23.4</v>
+        <v>123.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1778,88 +1720,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2577.7</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1291.6</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>2726.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>82.8</v>
+        <v>182.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.2</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>35.3</v>
+        <v>97.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-14
-</t>
-        </is>
+        <v>56.2</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>189.9</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>2952.9</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>2121.5</v>
+        <v>2212</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>54.7</v>
+        <v>1154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.6</v>
+        <v>1083.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>820.6</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-7918949
-</t>
-        </is>
+        <v>182</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>1131</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>48.3</v>
+        <v>148.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>148.8</v>
+        <v>11245.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>19.1</v>
+        <v>1124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1875,75 +1803,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>2.6</v>
+        <v>315.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>6.8</v>
+        <v>16</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.7</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N17" s="3" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>60.9</v>
+        <v>942.5</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>72.3</v>
+        <v>4.7</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>87.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.2</v>
+        <v>37.6</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>212.1</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>44.9</v>
-      </c>
+        <v>229.2</v>
+      </c>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1957,77 +1881,73 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
-2
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F18" s="9" t="n"/>
+      <c r="C18" s="3" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>22.7</v>
+      </c>
       <c r="G18" s="3" t="n">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.4</v>
+        <v>16.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>7.6</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>5.9</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>911.1</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>166.9</v>
+        <v>115.5</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>14.4</v>
+        <v>40.4</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="8" t="n">
+        <v>184.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2042,18 +1962,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-2975
-</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>12.9</v>
+      <c r="C19" s="3" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
@@ -2062,29 +1978,27 @@
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>60.8</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
@@ -2093,27 +2007,27 @@
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>96.2</v>
-      </c>
+        <v>112.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr"/>
       <c r="W19" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>29.7</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2127,56 +2041,51 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>12.3</v>
+      <c r="C20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="11" t="inlineStr"/>
+      <c r="E20" s="8" t="n">
+        <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L20" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5</v>
+        <v>522</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>10.6</v>
+      <c r="R20" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2185,21 +2094,23 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>12.4</v>
+        <v>29.8</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>182.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2217,42 +2128,40 @@
         <v>542.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>1.1</v>
+        <v>30.2</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>36.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G21" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>1.6</v>
+        <v>13.2</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>12.7</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>77.5</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="P21" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2262,28 +2171,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1.6</v>
+        <v>17.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>12.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2299,75 +2208,75 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
+        <v>1536.3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.1</v>
+        <v>34.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>13.3</v>
+      <c r="H22" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M22" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>21.1</v>
+        <v>51</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>6.8</v>
+        <v>16.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>216.3</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>126.2</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2381,79 +2290,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="10" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>17.1</v>
+      <c r="C23" s="3" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44255
-82947
-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.2</v>
+        <v>719.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.1</v>
+        <v>20.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>23</v>
+        <v>1212</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.4</v>
+        <v>141.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.4</v>
+        <v>154.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>4.9</v>
+        <v>182.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>292</v>
+        <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>30.5</v>
+        <v>1302.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>68.8</v>
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>17.3</v>
+        <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>192.1</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2469,76 +2376,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5026.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>78.40000000000001</v>
+      <c r="E24" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J24" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J24" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>54.6</v>
+        <v>4.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>87.2</v>
+        <v>116.6</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>37.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2554,79 +2457,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>12.2</v>
+        <v>425.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>11.8</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>14</v>
+        <v>140</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>114</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-2
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-171111
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>1</v>
+        <v>911.1</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>1457.5</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>1112.1</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2646,70 +2543,68 @@
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>24.8</v>
+      <c r="E26" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>22.5</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>15</v>
+      <c r="H26" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>72.3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K26" s="8" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L26" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>20.2</v>
+        <v>18</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.8</v>
+        <v>33.4</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>26.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>227</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>125</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2724,80 +2619,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>28.58</v>
+        <v>550.1</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>98.5</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>528</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>29.3</v>
+        <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>7.1</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>3.4</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>37.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>1026.6</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2813,80 +2696,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>621</v>
+        <v>1621</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>6.5</v>
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>28.1</v>
+        <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>20</v>
+        <v>10.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>1.8</v>
+      <c r="M28" s="8" t="n">
+        <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.8</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>428</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>1428</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>120.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>30.8</v>
+        <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>13.4</v>
+        <v>0.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>166</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="V28" s="8" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W28" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.9</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
+        <v>18.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>30.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2902,75 +2781,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>4.6</v>
+        <v>624.9</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>12.2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>23.9</v>
+        <v>29.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>20.4</v>
+        <v>17.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>6</v>
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.3</v>
+        <v>141.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4.6</v>
+        <v>45.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n">
+        <v>3068.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2985,75 +2864,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>2.3</v>
+        <v>2781.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.1</v>
+        <v>187.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.5</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>32</v>
+        <v>372</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>55.8</v>
+        <v>155.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>110.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>6.3</v>
+        <v>130.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.3</v>
+        <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>33.5</v>
+        <v>153.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.4</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>8194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>6.8</v>
+        <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3068,71 +2943,65 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>556.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>18</v>
+      <c r="E31" s="9" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4</v>
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5</v>
+        <v>11.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J31" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>43.1</v>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>155.1</v>
+        <v>31</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>14.2</v>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="n">
+        <v>114.5</v>
+      </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="W31" s="3" t="n">
+      <c r="V31" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="W31" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.5</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3150,70 +3019,68 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>1232.1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>424.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>17.1</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="n">
+        <v>31.9</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3227,74 +3094,72 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="11" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="C33" s="3" t="n">
+        <v>448.7</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>35.8</v>
+        <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>5.7</v>
+      <c r="M33" s="8" t="n">
+        <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="R33" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="8" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="8" t="n">
+        <v>218</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3312,77 +3177,69 @@
         <v>386.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>1.1</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>6</v>
+        <v>14.2</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0.8</v>
+      <c r="M34" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>116</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>52.2</v>
+        <v>12952.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>30.3</v>
+        <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+      <c r="X34" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-178
-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3400,62 +3257,58 @@
       <c r="C35" s="3" t="n">
         <v>433.9</v>
       </c>
-      <c r="D35" s="11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>12.4</v>
+      <c r="D35" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>14.2</v>
+        <v>5.3</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>10.3</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>2.1</v>
+        <v>124</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>55</v>
+        <v>222.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
@@ -3464,9 +3317,11 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>1839.8</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>422.1</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3481,73 +3336,71 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>22.2</v>
+        <v>341.3</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>30.3</v>
+        <v>25.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>23.7</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="3" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="n">
-        <v>9.1</v>
+        <v>21.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="M36" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>29.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R36" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>22.8</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>21.6</v>
+        <v>0.1</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="W36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>218.8</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>116.8</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3561,71 +3414,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>18.5</v>
+      <c r="C37" s="3" t="n">
+        <v>966.1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1181.6</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>1110.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.2</v>
+        <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>42.4</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>101</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>36.4</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>821.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>123.2</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>20.2</v>
+        <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.8</v>
+        <v>594.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>24.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.2</v>
+        <v>1782.6</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>4.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>34.1</v>
+        <v>1141</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.4</v>
+        <v>1134.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>79</v>
+        <v>0.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>49.2</v>
+        <v>949.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>183.1</v>
+        <v>181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>96.2</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3641,73 +3500,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>16.3</v>
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>5.8</v>
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>111.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>36.1</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>47.8</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>1418</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>59.8</v>
+        <v>16.9</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>33.5</v>
+        <v>26.7</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>48.5</v>
+        <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>9.5</v>
+        <v>940.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>28.9</v>
+        <v>30.8</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>37.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3726,47 +3581,45 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.4</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>6.5</v>
+        <v>314.6</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>80</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>15.5</v>
@@ -3775,25 +3628,23 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="X39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>36.4</v>
+        <v>396.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>22.2</v>
+        <v>226.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3809,74 +3660,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6.4</v>
+        <v>617.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>51.2</v>
+        <v>30.3</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>2622.17</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2.2</v>
+        <v>18.3</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>16.2</v>
+      </c>
       <c r="M40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>94.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>15.5</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>1.1</v>
+        <v>19</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="8" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>21</v>
+        <v>8120.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.6</v>
+        <v>1221.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3892,76 +3743,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>2.7</v>
+        <v>587.5</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>34.01000000000001</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5.6</v>
+        <v>16.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>16.2</v>
+        <v>10.8</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>18.8</v>
+        <v>49</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>15</v>
+        <v>29.8</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>15.3</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>26</v>
+        <v>122.2</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>28.9</v>
+        <v>128.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3976,81 +3825,75 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-4811
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E42" s="3" t="n">
+      <c r="C42" s="3" t="n">
+        <v>481.1</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="n">
+        <v>920.9</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="R42" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>45.5</v>
-      </c>
       <c r="S42" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>2.6</v>
+        <v>28.1</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>5.8</v>
+        <v>192.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.4</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4066,74 +3909,72 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>23.9</v>
+        <v>354</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>14.2</v>
+      <c r="F43" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8.5</v>
+        <v>19.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>10.9</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>98.5</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="R43" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>9.9</v>
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>28.7</v>
+        <v>201.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>24.6</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>41.8</v>
+        <v>13.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>285.3</v>
+        <v>1925.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>16.5</v>
+        <v>246.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4149,76 +3990,72 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>23.5</v>
+        <v>238</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>17.7</v>
+        <v>15.7</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>16.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>581.5</v>
+        <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>89.8</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>21.8</v>
+        <v>109.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>1.4</v>
+        <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>8.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.6</v>
+        <v>182.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4234,78 +4071,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>150.1</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>22.9</v>
+        <v>33102.9</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>11871.5</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>15.7</v>
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>119.1</v>
+        <v>11.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>6.1</v>
+        <v>82224.60000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>90.8</v>
+        <v>1512.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>3.5</v>
+        <v>1822.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>16.6</v>
+        <v>111011.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
+        <v>1815.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>0.4</v>
+        <v>11226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>22.2</v>
+        <v>133.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S45" s="3" t="n"/>
+        <v>1021.8</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>183.8</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>2.2</v>
+        <v>1836.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>52.8</v>
+        <v>8888.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.2</v>
+        <v>21462.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>14.7</v>
+        <v>106.1</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.2</v>
+        <v>1098.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-11
-</t>
-        </is>
+        <v>1222.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>1117.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4321,68 +4154,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>232.2</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>12.1</v>
+      </c>
       <c r="I46" s="3" t="n">
-        <v>35</v>
+        <v>6.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>524.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>8.6</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr"/>
       <c r="O46" s="3" t="n">
-        <v>26.5</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="R46" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>751.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>64.8</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -772,47 +772,55 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1569.8</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="8" t="n">
+        <v>562.8</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="8" t="n">
-        <v>72.8</v>
+      <c r="H4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>38.3</v>
+      <c r="Q4" s="3" t="n">
+        <v>33.3</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -837,74 +845,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
+        <v>15127.1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="E5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>21.8</v>
+      <c r="G5" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>44.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>65.5</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="8" t="n">
+      <c r="T5" s="3" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="8" t="n">
-        <v>10.3</v>
+      <c r="W5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>32.2</v>
+        <v>38.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -920,10 +930,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1504.8</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>34.8</v>
+        <v>2304.8</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>33.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
@@ -931,8 +941,8 @@
       <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>20623.1</v>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -944,25 +954,27 @@
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>89.8</v>
+        <v>6</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1140</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="8" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -972,22 +984,22 @@
         <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>41.8</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>14.2</v>
+      <c r="W6" s="8" t="n">
+        <v>64.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>201.2</v>
+        <v>20.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1011,10 +1023,10 @@
       <c r="E7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1024,53 +1036,55 @@
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>8</v>
+        <v>16.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>5.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>22.1</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="R7" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>8.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v>42.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>13.5</v>
+        <v>29.1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.4</v>
+        <v>23.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1086,37 +1100,41 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>485.1</v>
+        <v>11285.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+        <v>24.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
+        <v>81.2</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2</v>
+        <v>11</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>29.9</v>
+        <v>19.1</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>110.8</v>
+        <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>236.5</v>
+        <v>36</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1127,30 +1145,28 @@
       <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="8" t="n">
-        <v>71</v>
+      <c r="S8" s="3" t="n">
+        <v>87</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U8" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>45.1</v>
+      <c r="V8" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="W8" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="X8" s="8" t="n">
-        <v>11.7</v>
+      <c r="X8" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>11098.2</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1165,51 +1181,55 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>1169.7</v>
-      </c>
-      <c r="E9" s="9" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="F9" s="10" t="n">
+        <v>1413.4</v>
+      </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>39.1</v>
+        <v>329.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1644.2</v>
+        <v>614.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
+        <v>32.9</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>258.7</v>
+        <v>121.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>949.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1169</v>
+        <v>169</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
@@ -1218,7 +1238,7 @@
         <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1139.7</v>
+        <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>169.6</v>
@@ -1230,7 +1250,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1120.2</v>
+        <v>1158.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1248,72 +1268,70 @@
       <c r="C10" s="3" t="n">
         <v>231.2</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>331.6</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
+      <c r="D10" s="10" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
+        <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>99.8</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.4</v>
+        <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V10" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>17.8</v>
+      <c r="X10" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>99.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1329,33 +1347,37 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1427.8</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr"/>
-      <c r="F11" s="3" t="n">
-        <v>23.9</v>
+        <v>427.9</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>83.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.6</v>
+        <v>13.9</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>11.7</v>
+      </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16.4</v>
+        <v>61.4</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
@@ -1364,24 +1386,22 @@
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>148.9</v>
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>122</v>
+        <v>822</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>21.7</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1400,29 +1420,31 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.1</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>44.8</v>
+        <v>206.7</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>28.7</v>
+        <v>21.7</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="n">
+        <v>6.1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1431,22 +1453,22 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>1.6</v>
+        <v>53</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R12" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16.2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
@@ -1455,19 +1477,19 @@
         <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
+        <v>21.7</v>
       </c>
       <c r="W12" s="8" t="n">
         <v>84</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>47</v>
+        <v>1217</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>4.8</v>
+        <v>1835.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1483,19 +1505,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1601.3</v>
+        <v>601.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F13" s="8" t="n">
+      <c r="E13" s="9" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>18.9</v>
+      <c r="G13" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>11.4</v>
@@ -1503,11 +1525,11 @@
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
@@ -1517,40 +1539,40 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>1249</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q13" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>13.8</v>
+      <c r="R13" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U13" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1265.4</v>
+        <v>86.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1566,21 +1588,21 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F14" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G14" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1598,36 +1620,44 @@
       <c r="M14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="P14" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>7.3</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>161.1</v>
-      </c>
-      <c r="U14" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="V14" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>431.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1643,69 +1673,73 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1832.9</v>
+        <v>252.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>23.1</v>
+        <v>31.5</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>93.3</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>16.3</v>
+        <v>16.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>98</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T15" s="3" t="n">
         <v>115.4</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="n">
+        <v>820.8</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
-        <v>123.4</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1720,22 +1754,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1291.6</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>2726.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>82.09999999999999</v>
+        <v>237.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>182391.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>118.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>97.3</v>
@@ -1744,15 +1778,17 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>10.7</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>189.9</v>
+        <v>189.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2952.9</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>202.8</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="O16" s="3" t="n">
         <v>2212</v>
       </c>
@@ -1760,10 +1796,10 @@
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1154.7</v>
+        <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1083.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
@@ -1772,22 +1808,22 @@
         <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1188.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1131</v>
+        <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>172.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>148.3</v>
+        <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>11245.8</v>
+        <v>1143.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1124.4</v>
+        <v>1024.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1805,19 +1841,19 @@
       <c r="C17" s="3" t="n">
         <v>315.4</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>23.6</v>
+      <c r="D17" s="10" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>231.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
@@ -1827,15 +1863,17 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>942.5</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1844,19 +1882,19 @@
         <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>87.3</v>
+        <v>14.7</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>37.6</v>
+        <v>116.4</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>81.59999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>26.3</v>
+        <v>946.5</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>14.5</v>
@@ -1865,9 +1903,11 @@
         <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>229.2</v>
-      </c>
-      <c r="Z17" s="3" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1882,72 +1922,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>532.1</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>22.7</v>
+        <v>1032.1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>82.7</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>911.1</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>15.2</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="3" t="inlineStr"/>
+      <c r="V18" s="8" t="n">
+        <v>8.1</v>
+      </c>
       <c r="W18" s="8" t="n">
-        <v>184.4</v>
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1963,13 +2007,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
+        <v>596.5</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>12.3</v>
+        <v>35.4</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
@@ -1984,49 +2028,55 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>120.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>17.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>112.8</v>
+        <v>12.8</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr"/>
+        <v>61.4</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2042,49 +2092,51 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="11" t="inlineStr"/>
-      <c r="E20" s="8" t="n">
+        <v>9390.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>522</v>
+        <v>25</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2097,19 +2149,19 @@
         <v>29.8</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>22.2</v>
+        <v>620.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>182.4</v>
+        <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0.1</v>
+        <v>18.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>28.7</v>
+        <v>118.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2125,43 +2177,45 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.2</v>
+        <v>942.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>36.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G21" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
+      <c r="H21" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>77.5</v>
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>10.5</v>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P21" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2171,28 +2225,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>14.5</v>
+        <v>86.3</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>217.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2208,21 +2262,21 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1536.3</v>
+        <v>536.3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>34.8</v>
+        <v>31.8</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="G22" s="8" t="n">
+      <c r="F22" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2231,16 +2285,18 @@
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="8" t="n">
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
       </c>
@@ -2248,34 +2304,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>24.3</v>
+        <v>31.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="U22" s="8" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>216.3</v>
+        <v>26.3</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2291,22 +2347,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>160.3</v>
-      </c>
-      <c r="E23" s="9" t="n">
+        <v>2517.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>72.5</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>1117.1</v>
+      <c r="F23" s="10" t="n">
+        <v>13.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>86.8</v>
+        <v>186.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2318,49 +2374,49 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>719.1</v>
+        <v>1.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1212</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>141.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>154.4</v>
+        <v>134.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>13.5</v>
+        <v>73.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>36.6</v>
+        <v>56.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1302.6</v>
+        <v>138.8</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>1127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2376,47 +2432,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>309.5</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F24" s="9" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="8" t="n">
+      <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>4.6</v>
+        <v>34.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R24" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2431,17 +2491,15 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="W24" s="3" t="inlineStr"/>
       <c r="X24" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2457,25 +2515,25 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>425.5</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>43.2</v>
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="H25" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.9</v>
@@ -2483,34 +2541,38 @@
       <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="M25" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>911.1</v>
+        <v>4.2</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>148</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>87.3</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>120.2</v>
+        <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>17.7</v>
+        <v>42.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>7.7</v>
       </c>
       <c r="W25" s="8" t="n">
         <v>11</v>
@@ -2519,10 +2581,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1457.5</v>
+        <v>1411.4</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>21821828</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2538,53 +2600,55 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>530.4</v>
+        <v>230.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>15.5</v>
+      <c r="F26" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>5.5</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>11.6</v>
+        <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>182</v>
+        <v>812</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.1</v>
+        <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>18</v>
@@ -2592,18 +2656,20 @@
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Y26" s="3" t="n">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>125</v>
+        <v>25.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2621,35 +2687,39 @@
       <c r="C27" s="3" t="n">
         <v>550.1</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E27" s="8" t="n">
+      <c r="D27" s="9" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>23.5</v>
+      <c r="F27" s="9" t="n">
+        <v>23.56</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>16.6</v>
+        <v>26.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
-        <v>10.6</v>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>16.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O27" s="3" t="n">
         <v>22</v>
       </c>
@@ -2660,27 +2730,29 @@
         <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="T27" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="U27" s="8" t="n">
-        <v>37.4</v>
+      <c r="U27" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>1026.6</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.6</v>
+        <v>1865.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2696,21 +2768,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
+        <v>631</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F28" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H28" s="3" t="n">
+      <c r="G28" s="8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H28" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2720,37 +2792,37 @@
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1428</v>
+        <v>142</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>120.8</v>
+        <v>101</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.3</v>
+        <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>43.4</v>
+        <v>28.4</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
@@ -2765,7 +2837,7 @@
         <v>18.6</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>30.8</v>
+        <v>90.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2781,62 +2853,64 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
+        <v>624.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>34.4</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>12.2</v>
+        <v>22.1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>29.3</v>
+        <v>28.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>0.8</v>
+        <v>49.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>141.3</v>
+        <v>4.1</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Q29" s="8" t="n">
-        <v>83.5</v>
+      <c r="Q29" s="3" t="n">
+        <v>33.5</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>45.6</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>42.1</v>
+      </c>
       <c r="V29" s="8" t="n">
-        <v>27.7</v>
+        <v>75.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
@@ -2845,10 +2919,10 @@
         <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>18.6</v>
+        <v>118.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>3068.2</v>
+        <v>10.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2864,40 +2938,40 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>2181.9</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>161.6</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>714.5</v>
-      </c>
-      <c r="F30" s="9" t="n">
+      <c r="E30" s="10" t="n">
+        <v>726.5</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>187.1</v>
+        <v>181.1</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>372</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>155.8</v>
+        <v>139.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>110.9</v>
+        <v>118.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>130.6</v>
+        <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>222.3</v>
@@ -2906,17 +2980,19 @@
         <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>153.1</v>
+        <v>159.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="S30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>31.8</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>8194.1</v>
+        <v>1194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -2925,10 +3001,14 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>1190</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>42.9</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2943,19 +3023,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
+        <v>856.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
+      <c r="E31" s="10" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>17.4</v>
+        <v>4.8</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -2966,12 +3046,18 @@
       <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
@@ -2981,27 +3067,29 @@
       <c r="Q31" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="S31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T31" s="3" t="n">
-        <v>114.5</v>
+        <v>14.5</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W31" s="8" t="n">
+      <c r="V31" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3020,66 +3108,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>33.8</v>
+        <v>6144.4</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="8" t="n">
-        <v>1232.1</v>
+      <c r="G32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.6</v>
+        <v>62.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>94.2</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>126</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>33.6</v>
+      </c>
       <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="T32" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="8" t="n">
+      <c r="U32" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3095,15 +3193,15 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>448.7</v>
+        <v>613.7</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F33" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="G33" s="8" t="n">
@@ -3119,46 +3217,50 @@
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L33" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
+        <v>20.1</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="T33" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="U33" s="3" t="inlineStr"/>
+        <v>30.2</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
       <c r="V33" s="8" t="n">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>13.5</v>
+        <v>61.7</v>
       </c>
       <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>10.2</v>
+        <v>1455.4</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>1.3</v>
+        <v>103.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3174,21 +3276,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>386.6</v>
+        <v>3846.3</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F34" s="8" t="n">
+      <c r="E34" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3196,50 +3302,50 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>116</v>
+      <c r="N34" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>12952.2</v>
+        <v>42.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>13.4</v>
+        <v>32.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="X34" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>11.6</v>
+        <v>1860.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3255,29 +3361,31 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>433.9</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>30.3</v>
+        <v>439.9</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>50.3</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="11" t="inlineStr"/>
-      <c r="G35" s="8" t="n">
+      <c r="F35" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>28.5</v>
+        <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3285,42 +3393,44 @@
       <c r="M35" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>19.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>222.8</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V35" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1839.8</v>
+        <v>23</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>422.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3341,65 +3451,69 @@
       <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F36" s="11" t="inlineStr"/>
+      <c r="E36" s="11" t="inlineStr"/>
+      <c r="F36" s="12" t="n">
+        <v>18.7</v>
+      </c>
       <c r="G36" s="3" t="n">
-        <v>14.3</v>
+        <v>26.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J36" s="3" t="n">
-        <v>21.1</v>
+        <v>2.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L36" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>34.8</v>
+        <v>32.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v>822.1</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>218.8</v>
+        <v>1498.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3415,76 +3529,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>966.1</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>1181.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
+        <v>2216.6</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>168.9</v>
       </c>
-      <c r="F37" s="9" t="n">
-        <v>1110.2</v>
+      <c r="F37" s="10" t="n">
+        <v>11025.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>15.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>101</v>
+        <v>1018</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>36.4</v>
+        <v>8.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>123.2</v>
+        <v>23.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>594.1</v>
+        <v>593.5</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.5</v>
+        <v>133.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1782.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1141</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1134.2</v>
+        <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>114.1</v>
+        <v>111.3</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>0.6</v>
+        <v>87</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>949.8</v>
+        <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
+        <v>1315</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3500,57 +3614,61 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>443.3</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
+        <v>473.3</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>111.2</v>
+        <v>19.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M38" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>1418</v>
+        <v>18</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>940.1</v>
+        <v>12.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>26.9</v>
+        <v>20.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3581,48 +3699,52 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>314.6</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>21.7</v>
+        <v>914.6</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>141.26</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>21.19</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>51.2</v>
+        <v>0.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>13.2</v>
+        <v>510.1</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>15.5</v>
+        <v>211</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>59.3</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
@@ -3630,21 +3752,23 @@
       <c r="T39" s="3" t="n">
         <v>122.4</v>
       </c>
-      <c r="U39" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="8" t="n">
+      <c r="U39" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>226.6</v>
+        <v>28.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3660,31 +3784,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>2622.17</v>
+        <v>6471.6</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <v>8.6</v>
+      <c r="I40" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>16.2</v>
@@ -3693,7 +3817,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3704,30 +3828,32 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="U40" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="V40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="W40" s="8" t="n">
         <v>84.7</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>10.1</v>
+        <v>16.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>8120.6</v>
+        <v>38</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1221.6</v>
+        <v>2216.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3745,17 +3871,17 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="10" t="n">
-        <v>34.01000000000001</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>16.2</v>
+      <c r="D41" s="9" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>62.2</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>15.2</v>
+      <c r="G41" s="8" t="n">
+        <v>1662.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
@@ -3767,51 +3893,51 @@
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>10.1</v>
+      </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>15.3</v>
+      <c r="R41" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="V41" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>10.1</v>
+      <c r="X41" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1828.4</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3828,29 +3954,29 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>31.31</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>23.3</v>
+      <c r="D42" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H42" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>16.8</v>
@@ -3858,43 +3984,43 @@
       <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>920.9</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="R42" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>19.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>10.2</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3909,16 +4035,16 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>30.5</v>
+        <v>254</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>5.6</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="8" t="n">
-        <v>23.9</v>
+      <c r="F43" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="G43" s="8" t="n">
         <v>4.1</v>
@@ -3927,54 +4053,58 @@
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="M43" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="8" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>201.3</v>
+        <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>22.7</v>
+        <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1925.3</v>
+        <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>246.1</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3990,7 +4120,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.7</v>
@@ -3998,25 +4128,29 @@
       <c r="E44" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>22.9</v>
+      <c r="F44" s="9" t="n">
+        <v>22.29</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="8" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="8" t="n">
+      <c r="H44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>2.8</v>
+        <v>19.8</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>8.800000000000001</v>
@@ -4025,22 +4159,22 @@
         <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q44" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="R44" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>109.3</v>
+        <v>119.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>12.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
@@ -4049,13 +4183,13 @@
         <v>14.7</v>
       </c>
       <c r="X44" s="8" t="n">
-        <v>12.2</v>
+        <v>12.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>182.4</v>
+        <v>1122.1</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4070,76 +4204,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>33102.9</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>11871.5</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>191.9</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>1122.1</v>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="10" t="n">
+        <v>1555.1</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>1102.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>21</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.2</v>
+        <v>29.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>82224.60000000001</v>
+        <v>345</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1512.3</v>
+        <v>226.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1822.2</v>
+        <v>14.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>111011.1</v>
+        <v>1291.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1815.9</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>11226.5</v>
+        <v>102261.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
+        <v>920.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>133.4</v>
+        <v>128.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1021.8</v>
+        <v>11.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>183.8</v>
+        <v>182</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1836.9</v>
+        <v>126.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>8888.6</v>
+        <v>102.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21462.1</v>
+        <v>141.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>106.1</v>
+        <v>101</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1098.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.8</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>1117.2</v>
-      </c>
+        <v>1222.4</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4156,63 +4288,69 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="10" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E46" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>23</v>
+      <c r="F46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>119.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>11</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>28.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>119.6</v>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -159,6 +165,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,13 +781,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>562.8</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>569.8</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>93.7</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>21.6</v>
@@ -787,7 +796,7 @@
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -802,10 +811,10 @@
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>34.5</v>
@@ -814,9 +823,9 @@
         <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R4" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -845,40 +854,40 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>15127.1</v>
+        <v>648.3</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>10</v>
+      <c r="E5" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>28.8</v>
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>22.2</v>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -896,10 +905,10 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>444.9</v>
+        <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
@@ -911,10 +920,10 @@
         <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>38.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -930,7 +939,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2304.8</v>
+        <v>306.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>33.9</v>
@@ -938,35 +947,35 @@
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="G6" s="8" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.8</v>
+        <v>2.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>2109.8</v>
+        <v>100.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>8.5</v>
@@ -978,28 +987,28 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>41.8</v>
+      <c r="U6" s="8" t="n">
+        <v>91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="8" t="n">
-        <v>64.2</v>
+      <c r="W6" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>20.2</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,25 +1039,25 @@
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1057,34 +1066,34 @@
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.7</v>
+        <v>34.7</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>13.8</v>
+        <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>1.7</v>
+        <v>21.7</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.5</v>
+        <v>86.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>23.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1100,7 +1109,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>11285.1</v>
+        <v>285.1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
@@ -1108,8 +1117,8 @@
       <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>82.8</v>
+      <c r="F8" s="3" t="n">
+        <v>22.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>23.4</v>
@@ -1118,23 +1127,23 @@
         <v>11.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>81.2</v>
+        <v>0.4</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>16.1</v>
+      <c r="K8" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>36</v>
+        <v>3262</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1146,7 +1155,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1154,17 +1163,17 @@
       <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W8" s="8" t="n">
+      <c r="V8" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>11098.2</v>
+        <v>10.2</v>
       </c>
       <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1181,37 +1190,35 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2666</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>169.7</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1413.4</v>
-      </c>
+        <v>19656.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1169.7</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr"/>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>329.1</v>
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>614.2</v>
+        <v>14.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>121.7</v>
@@ -1220,7 +1227,7 @@
         <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>169</v>
@@ -1250,7 +1257,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1158.4</v>
+        <v>120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1266,22 +1273,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>231.2</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>22.3</v>
+        <v>531.2</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1301,7 +1308,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
@@ -1310,13 +1317,13 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="U10" s="8" t="n">
-        <v>94.8</v>
+      <c r="U10" s="3" t="n">
+        <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.9</v>
@@ -1324,11 +1331,11 @@
       <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>99.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8</v>
@@ -1349,37 +1356,39 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>8</v>
+      <c r="D11" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>83.8</v>
+      <c r="F11" s="10" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H11" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>113</v>
       </c>
@@ -1389,17 +1398,17 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>14.9</v>
+      <c r="R11" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>822</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
@@ -1422,16 +1431,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="D12" s="10" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1462,19 +1469,19 @@
         <v>10</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.7</v>
@@ -1483,13 +1490,13 @@
         <v>84</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>12.9</v>
+        <v>62.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1217</v>
+        <v>1417</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>1835.8</v>
+        <v>18.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1510,20 +1517,18 @@
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>59.4</v>
+      <c r="E13" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="G13" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>849</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
@@ -1548,7 +1553,7 @@
         <v>33.2</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1562,17 +1567,17 @@
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="X13" s="8" t="n">
-        <v>2.1</v>
+      <c r="X13" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>86.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1594,13 +1599,13 @@
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.4</v>
+        <v>17.8</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>24.4</v>
+      <c r="G14" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13.6</v>
@@ -1612,16 +1617,16 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>49</v>
@@ -1633,10 +1638,10 @@
         <v>30.3</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>73.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
@@ -1650,14 +1655,14 @@
       <c r="W14" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="X14" s="8" t="n">
-        <v>81.2</v>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>80.8</v>
+        <v>1020.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>31.2</v>
+        <v>231.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1673,19 +1678,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>252.1</v>
+        <v>2652.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>93.3</v>
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
@@ -1702,41 +1707,39 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4.8</v>
+        <v>148.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q15" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="8" t="n">
+        <v>0.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>820.8</v>
+        <v>15.4</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y15" s="3" t="inlineStr"/>
       <c r="Z15" s="3" t="inlineStr"/>
@@ -1754,16 +1757,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>182391.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>118.2</v>
+        <v>257.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>8291.6</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1778,25 +1781,23 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>189.8</v>
-      </c>
+        <v>11.7</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="n">
-        <v>202.8</v>
+        <v>22.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212</v>
+        <v>2212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>184.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1805,22 +1806,22 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>188.2</v>
+        <v>128.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>172.8</v>
+        <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1143.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1024.4</v>
@@ -1839,19 +1840,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>231.6</v>
+        <v>2313.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1862,18 +1863,20 @@
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
+      <c r="K17" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1885,13 +1888,13 @@
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>116.4</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>81.59999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>946.5</v>
@@ -1906,7 +1909,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>24.9</v>
+        <v>29.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1922,28 +1925,26 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1032.1</v>
+        <v>232.1</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F18" s="9" t="n">
+      <c r="E18" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="10" t="n">
         <v>82.7</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1955,7 +1956,7 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
@@ -1964,34 +1965,34 @@
         <v>6.6</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.5</v>
+        <v>118.3</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>8.1</v>
+        <v>28.1</v>
       </c>
       <c r="W18" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2007,13 +2008,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.5</v>
+        <v>596.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.3</v>
+        <v>33.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>22.9</v>
@@ -2024,23 +2025,21 @@
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>120.6</v>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>12.5</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>17.1</v>
+        <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>60.5</v>
@@ -2055,16 +2054,16 @@
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>61.4</v>
+      <c r="U19" s="3" t="n">
+        <v>41.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
@@ -2073,10 +2072,10 @@
         <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2092,13 +2091,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9390.5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>17.2</v>
+        <v>322.8</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>4.8</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
@@ -2106,29 +2105,29 @@
       <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>11.1</v>
+      <c r="N20" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2143,22 +2142,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.5</v>
+        <v>44.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="8" t="n">
-        <v>620.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>18.7</v>
+        <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>118.2</v>
@@ -2177,16 +2176,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>942.2</v>
+        <v>42.2</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>16.4</v>
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>14.5</v>
@@ -2195,7 +2194,7 @@
         <v>11.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>10.6</v>
@@ -2203,8 +2202,8 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>17.7</v>
+      <c r="L21" s="8" t="n">
+        <v>75.7</v>
       </c>
       <c r="M21" s="8" t="n">
         <v>11.5</v>
@@ -2237,16 +2236,16 @@
         <v>86.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>217.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2262,7 +2261,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
+        <v>936.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
@@ -2270,8 +2269,8 @@
       <c r="E22" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>12.5</v>
+      <c r="F22" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>16.6</v>
@@ -2295,7 +2294,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
@@ -2313,19 +2312,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="8" t="n">
         <v>39</v>
       </c>
       <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>14.6</v>
+      <c r="W22" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2349,20 +2348,20 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>13.1</v>
+      <c r="D23" s="9" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1117.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>186.8</v>
+        <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2374,28 +2373,28 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>4.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>1272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>134.4</v>
+        <v>254.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.5</v>
+        <v>23.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>56.6</v>
+        <v>368.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2404,10 +2403,10 @@
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.8</v>
+        <v>138.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>168.8</v>
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>42.8</v>
@@ -2416,7 +2415,7 @@
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1127.4</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2432,49 +2431,47 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>543.5</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E24" s="10" t="n">
+        <v>503.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="J24" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>10.1</v>
+        <v>18.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.6</v>
+        <v>24.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.9</v>
+        <v>20.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>14.7</v>
@@ -2483,7 +2480,7 @@
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>37.4</v>
@@ -2491,15 +2488,17 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2523,7 +2522,7 @@
       <c r="E25" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="13" t="n">
         <v>24.8</v>
       </c>
       <c r="G25" s="8" t="n">
@@ -2545,46 +2544,46 @@
         <v>19.8</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>21.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
+        <v>401</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>4.2</v>
+        <v>29.4</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>87.3</v>
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>37.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>42.8</v>
+        <v>12.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1411.4</v>
+        <v>41.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>21821828</v>
+        <v>1112.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2599,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>230.4</v>
+        <v>530.4</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>30.3</v>
@@ -2608,11 +2607,11 @@
       <c r="E26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <v>5.5</v>
+      <c r="G26" s="3" t="n">
+        <v>85.5</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>21.6</v>
@@ -2636,30 +2635,30 @@
         <v>1.9</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>812</v>
+        <v>82</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="3" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2669,7 +2668,7 @@
         <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>25.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2685,19 +2684,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>31.18</v>
+        <v>50.1</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>31.84</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>23.56</v>
+      <c r="F27" s="13" t="n">
+        <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>26.1</v>
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
@@ -2706,25 +2705,25 @@
         <v>6.8</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>67.90000000000001</v>
+      <c r="L27" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
@@ -2736,23 +2735,25 @@
         <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>31.4</v>
+        <v>16</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
+        <v>28.2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="X27" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1865.9</v>
+        <v>196.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2768,22 +2769,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>631</v>
+        <v>1621</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="F28" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F28" s="13" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>81.59999999999999</v>
+      <c r="G28" s="3" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2804,30 +2805,30 @@
         <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>142</v>
+        <v>48</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>32.1</v>
+        <v>803.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>68.09999999999999</v>
+        <v>29.4</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>43.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2836,9 +2837,7 @@
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v>90.8</v>
-      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2858,11 +2857,11 @@
       <c r="D29" s="3" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="8" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>28.3</v>
+      <c r="E29" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
@@ -2871,13 +2870,13 @@
         <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>10</v>
+        <v>49.3</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>181.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2889,13 +2888,13 @@
         <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.1</v>
+        <v>41.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.5</v>
+        <v>83.5</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>14</v>
@@ -2907,22 +2906,22 @@
         <v>19</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>75.7</v>
+        <v>47.1</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>10.8</v>
+        <v>23009</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2938,28 +2937,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2181.9</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>726.5</v>
-      </c>
-      <c r="F30" s="10" t="n">
+        <v>2281.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1561.6</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>181.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>139.8</v>
+        <v>23.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>118.9</v>
@@ -2977,22 +2976,22 @@
         <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.7</v>
+        <v>91.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>159.1</v>
+        <v>155.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>12.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -3001,13 +3000,13 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1190</v>
+        <v>110</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>13.6</v>
+        <v>106.9</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>42.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3023,19 +3022,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>856.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="13" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.8</v>
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -3043,11 +3042,11 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3071,7 +3070,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3108,37 +3107,37 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>6144.4</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>0.8</v>
+        <v>61.1</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="13" t="n">
         <v>22.2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>62.1</v>
+        <v>6.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>126</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1.2</v>
@@ -3147,12 +3146,12 @@
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3164,20 +3163,20 @@
       <c r="U32" s="3" t="n">
         <v>47.4</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="8" t="n">
         <v>28.3</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3193,31 +3192,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>613.7</v>
+        <v>122.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F33" s="12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F33" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
@@ -3229,38 +3228,40 @@
         <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>61.7</v>
+      <c r="W33" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1455.4</v>
+        <v>149.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>103.9</v>
+        <v>43.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3276,7 +3277,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3846.3</v>
+        <v>386.6</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.8</v>
@@ -3284,14 +3285,14 @@
       <c r="E34" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="13" t="n">
         <v>23.2</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.8</v>
+        <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.5</v>
@@ -3302,17 +3303,17 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.4</v>
+      <c r="M34" s="8" t="n">
+        <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>42.2</v>
+        <v>22.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3320,11 +3321,11 @@
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>32.4</v>
+      <c r="R34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
@@ -3332,20 +3333,20 @@
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>89</v>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>11.8</v>
+        <v>18.7</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1860.6</v>
+        <v>1801.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3363,28 +3364,28 @@
       <c r="C35" s="3" t="n">
         <v>439.9</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="10" t="n">
         <v>50.3</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="13" t="n">
         <v>23.7</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
@@ -3394,18 +3395,16 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="R35" s="8" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3414,8 +3413,8 @@
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U35" s="8" t="n">
-        <v>11.1</v>
+      <c r="U35" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3427,11 +3426,9 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>19.2</v>
-      </c>
+        <v>2121.5</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3451,25 +3448,21 @@
       <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="11" t="inlineStr"/>
-      <c r="F36" s="12" t="n">
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="13" t="n">
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="H36" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3477,10 +3470,10 @@
         <v>12.3</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3495,13 +3488,13 @@
         <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.4</v>
+        <v>2.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>822.1</v>
+      <c r="V36" s="3" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="W36" s="8" t="n">
         <v>13.6</v>
@@ -3510,10 +3503,10 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1498.8</v>
+        <v>1186</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>116.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3531,74 +3524,74 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="E37" s="10" t="n">
+      <c r="D37" s="9" t="n">
+        <v>11810.6</v>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>168.9</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>11025.3</v>
+      <c r="F37" s="9" t="n">
+        <v>110.2</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>15.8</v>
+        <v>33.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1018</v>
+        <v>180</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>593.5</v>
+        <v>89.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>151.6</v>
+        <v>1151</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111.3</v>
+        <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>1315</v>
+        <v>1181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3614,22 +3607,22 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>19.2</v>
+      <c r="G38" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
@@ -3643,32 +3636,32 @@
       <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.2</v>
+        <v>27.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3701,71 +3694,71 @@
       <c r="C39" s="3" t="n">
         <v>914.6</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>141.26</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>21.19</v>
+      <c r="D39" s="10" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>18.66</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>210.1</v>
+        <v>811</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>510.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>59.3</v>
+      <c r="Q39" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>96.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>28.8</v>
@@ -3784,25 +3777,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6471.6</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>91.7</v>
+        <v>641.4</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>90.7</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
@@ -3817,7 +3810,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3828,7 +3821,7 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="8" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3837,23 +3830,23 @@
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>94.2</v>
+      <c r="U40" s="3" t="n">
+        <v>84.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.1</v>
+      <c r="W40" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2216.3</v>
+        <v>6.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3871,29 +3864,29 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>62.2</v>
+      <c r="D41" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>1662.1</v>
+      <c r="G41" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>18</v>
@@ -3905,10 +3898,10 @@
         <v>10.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>19.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
@@ -3920,24 +3913,24 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>22.2</v>
+        <v>122.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12.6</v>
+        <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
       <c r="X41" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="Y41" s="3" t="n">
-        <v>1828.4</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3954,23 +3947,23 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>1.6</v>
+      <c r="D42" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="G42" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>7.3</v>
@@ -3978,32 +3971,32 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
@@ -4011,14 +4004,14 @@
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>13</v>
+      <c r="W42" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4035,10 +4028,10 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>5.6</v>
+        <v>534</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>30.2</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>16.4</v>
@@ -4050,7 +4043,7 @@
         <v>4.1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>13.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4064,14 +4057,14 @@
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>921.6</v>
+        <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
@@ -4079,7 +4072,7 @@
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4089,13 +4082,13 @@
         <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4104,7 +4097,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.6</v>
+        <v>124.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4125,11 +4118,11 @@
       <c r="D44" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="9" t="n">
-        <v>22.29</v>
+      <c r="F44" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>15.7</v>
@@ -4144,19 +4137,19 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>10.6</v>
@@ -4164,33 +4157,31 @@
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>7.8</v>
+        <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>12.8</v>
+        <v>112.3</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="8" t="n">
+      <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>12.8</v>
+      <c r="X44" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>1122.1</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4204,72 +4195,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
-        <v>1555.1</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>411.9</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>1102.1</v>
+      <c r="C45" s="3" t="n">
+        <v>1801.1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>345</v>
+        <v>721.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>226.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>14.8</v>
+        <v>181.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1291.9</v>
+        <v>1281.8</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>102261.5</v>
+        <v>1226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>920.4</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>128.4</v>
+        <v>170</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>11.8</v>
+        <v>81.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>102.6</v>
-      </c>
+        <v>126.4</v>
+      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="n">
-        <v>141.2</v>
+        <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>101</v>
+        <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.4</v>
+        <v>1222.9</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4286,30 +4277,32 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>1</v>
+        <v>561.8</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>83</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -4320,7 +4313,7 @@
         <v>9.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>119.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4329,7 +4322,7 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
@@ -4338,22 +4331,22 @@
         <v>22.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>84.8</v>
+        <v>24</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>14.4</v>
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>112.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -807,7 +807,7 @@
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="12" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -835,8 +835,8 @@
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="13" t="inlineStr"/>
+      <c r="W4" s="13" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -880,7 +880,7 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="12" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -898,7 +898,7 @@
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="10" t="n">
         <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -965,7 +965,7 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="12" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -998,7 +998,7 @@
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="10" t="n">
         <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1050,7 +1050,7 @@
       <c r="K7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="12" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
@@ -1068,7 +1068,7 @@
       <c r="Q7" s="3" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="10" t="n">
         <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1083,7 +1083,7 @@
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1135,7 +1135,7 @@
       <c r="K8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="M8" s="8" t="n">
@@ -1211,13 +1211,13 @@
       <c r="J9" s="3" t="n">
         <v>168.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="9" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1229,10 +1229,10 @@
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>169</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1244,10 +1244,10 @@
       <c r="U9" s="3" t="n">
         <v>1224.1</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1297,10 +1297,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="9" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
       <c r="P10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1325,10 +1325,10 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1383,7 +1383,7 @@
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="12" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1410,8 +1410,8 @@
       <c r="U11" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="W11" s="13" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       <c r="D12" s="10" t="n">
         <v>51.3</v>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
@@ -1456,7 +1456,7 @@
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1486,7 +1486,7 @@
       <c r="V12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="10" t="n">
         <v>84</v>
       </c>
       <c r="X12" s="8" t="n">
@@ -1539,7 +1539,7 @@
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1637,7 +1637,7 @@
       <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="10" t="n">
         <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1707,7 +1707,7 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="12" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1722,7 +1722,7 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="inlineStr"/>
+      <c r="R15" s="13" t="inlineStr"/>
       <c r="S15" s="8" t="n">
         <v>0.8</v>
       </c>
@@ -1732,7 +1732,7 @@
       <c r="U15" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="10" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="W15" s="8" t="n">
@@ -1780,11 +1780,11 @@
       <c r="J16" s="3" t="n">
         <v>56.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="n">
+      <c r="L16" s="11" t="inlineStr"/>
+      <c r="M16" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1796,10 +1796,10 @@
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>184.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1811,10 +1811,10 @@
       <c r="U16" s="3" t="n">
         <v>128.2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>131.3</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1869,7 +1869,7 @@
       <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="12" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1881,10 +1881,10 @@
       <c r="P17" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1896,10 +1896,10 @@
       <c r="U17" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>946.5</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1952,7 +1952,7 @@
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="12" t="n">
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1964,10 +1964,10 @@
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="10" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2032,10 +2032,10 @@
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="10" t="n">
         <v>63.5</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="12" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2050,7 +2050,7 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2062,7 +2062,7 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="10" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2120,7 +2120,7 @@
       <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="12" t="n">
         <v>12.6</v>
       </c>
       <c r="N20" s="8" t="n">
@@ -2135,7 +2135,7 @@
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="12" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2202,10 +2202,10 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="10" t="n">
         <v>75.7</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="12" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2220,7 +2220,7 @@
       <c r="Q21" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2232,10 +2232,10 @@
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="10" t="n">
         <v>86.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2290,7 +2290,7 @@
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="12" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2305,7 +2305,7 @@
       <c r="Q22" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2369,13 +2369,13 @@
       <c r="J23" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="12" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2387,10 +2387,10 @@
       <c r="P23" s="3" t="n">
         <v>41.3</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="9" t="n">
         <v>254.4</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2402,10 +2402,10 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="9" t="n">
         <v>138.6</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2455,10 +2455,10 @@
         <v>17.4</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2470,10 +2470,10 @@
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="12" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2485,10 +2485,10 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>1.6</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2522,7 +2522,7 @@
       <c r="E25" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="G25" s="8" t="n">
@@ -2558,7 +2558,7 @@
       <c r="Q25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S25" s="8" t="n">
@@ -2570,7 +2570,7 @@
       <c r="U25" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="10" t="n">
         <v>3.7</v>
       </c>
       <c r="W25" s="3" t="n">
@@ -2607,7 +2607,7 @@
       <c r="E26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="12" t="n">
         <v>22.1</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2640,10 +2640,10 @@
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>99.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2692,7 +2692,7 @@
       <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="12" t="n">
         <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2728,7 +2728,7 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2743,7 +2743,7 @@
       <c r="V27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2777,7 +2777,7 @@
       <c r="E28" s="8" t="n">
         <v>37.6</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="G28" s="3" t="n">
@@ -2810,10 +2810,10 @@
       <c r="P28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>803.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2860,7 +2860,7 @@
       <c r="E29" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="12" t="n">
         <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
@@ -2893,10 +2893,10 @@
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>83.5</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2960,13 +2960,13 @@
       <c r="J30" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>118.9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2978,10 +2978,10 @@
       <c r="P30" s="3" t="n">
         <v>91.7</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>155.1</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2993,10 +2993,10 @@
       <c r="U30" s="3" t="n">
         <v>194.1</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="9" t="n">
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3030,7 +3030,7 @@
       <c r="E31" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="12" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3048,10 +3048,10 @@
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>110.1</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3063,10 +3063,10 @@
       <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3078,10 +3078,10 @@
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3115,7 +3115,7 @@
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="12" t="n">
         <v>22.2</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3133,7 +3133,7 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="10" t="n">
         <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3200,7 +3200,7 @@
       <c r="E33" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3285,7 +3285,7 @@
       <c r="E34" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="12" t="n">
         <v>23.2</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3306,7 +3306,7 @@
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="10" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3370,7 +3370,7 @@
       <c r="E35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="12" t="n">
         <v>23.7</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3403,7 +3403,7 @@
       <c r="P35" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="Q35" s="13" t="inlineStr"/>
       <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
@@ -3448,8 +3448,8 @@
       <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="12" t="inlineStr"/>
-      <c r="F36" s="13" t="n">
+      <c r="E36" s="13" t="inlineStr"/>
+      <c r="F36" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3462,7 +3462,7 @@
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3493,7 +3493,7 @@
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="10" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="W36" s="8" t="n">
@@ -3545,13 +3545,13 @@
       <c r="J37" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3563,10 +3563,10 @@
       <c r="P37" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>133.5</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3578,10 +3578,10 @@
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="9" t="n">
         <v>114.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3615,7 +3615,7 @@
       <c r="E38" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F38" s="12" t="n">
         <v>22.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3633,10 +3633,10 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3648,10 +3648,10 @@
       <c r="P38" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3663,10 +3663,10 @@
       <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3718,7 +3718,7 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="12" t="n">
         <v>15.1</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3733,7 +3733,7 @@
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3748,7 +3748,7 @@
       <c r="U39" s="8" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3803,7 +3803,7 @@
       <c r="K40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3818,7 +3818,7 @@
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>30</v>
       </c>
       <c r="R40" s="8" t="n">
@@ -3833,7 +3833,7 @@
       <c r="U40" s="3" t="n">
         <v>84.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3888,7 +3888,7 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="L41" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M41" s="8" t="n">
@@ -3903,7 +3903,7 @@
       <c r="P41" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>29.8</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3918,7 +3918,7 @@
       <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="12" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3971,7 +3971,7 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="M42" s="8" t="n">
@@ -3986,7 +3986,7 @@
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4001,7 +4001,7 @@
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="12" t="n">
         <v>18</v>
       </c>
       <c r="W42" s="8" t="n">
@@ -4054,7 +4054,7 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="12" t="n">
         <v>17.7</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4069,7 +4069,7 @@
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="12" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4084,7 +4084,7 @@
       <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="12" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
@@ -4139,10 +4139,10 @@
       <c r="K44" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="10" t="n">
         <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4154,7 +4154,7 @@
       <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="12" t="n">
         <v>29.2</v>
       </c>
       <c r="R44" s="3" t="n">
@@ -4169,7 +4169,7 @@
       <c r="U44" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4219,13 +4219,13 @@
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>181.2</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>1281.8</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4237,10 +4237,10 @@
       <c r="P45" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="9" t="n">
         <v>81.5</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4250,10 +4250,10 @@
         <v>126.4</v>
       </c>
       <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>144.2</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4303,10 +4303,10 @@
       <c r="K46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="9" t="n">
         <v>80.8</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4318,10 +4318,10 @@
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="12" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4333,10 +4333,10 @@
       <c r="U46" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,8 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -55,18 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +152,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -783,20 +786,20 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -805,38 +808,38 @@
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>23.7</v>
+        <v>1.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
+      <c r="Q4" s="9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R4" s="9" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>11.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="13" t="inlineStr"/>
-      <c r="W4" s="13" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr"/>
+      <c r="W4" s="12" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -854,18 +857,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>648.3</v>
-      </c>
-      <c r="D5" s="3" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="11" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -878,49 +881,47 @@
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>15.5</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="10" t="n">
-        <v>84</v>
+      <c r="R5" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>16.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="U5" s="11" t="n">
+        <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -939,67 +940,65 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>306.8</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>504.8</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>33.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>23.1</v>
+      <c r="G6" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>100.8</v>
+        <v>140</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="8" t="n">
-        <v>91</v>
+      <c r="U6" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="10" t="n">
-        <v>4.1</v>
+      <c r="W6" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
@@ -1008,7 +1007,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>20.2</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1026,20 +1025,20 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="9" t="n">
         <v>35.3</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="11" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1048,16 +1047,16 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1065,35 +1064,35 @@
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="10" t="n">
-        <v>3.2</v>
+      <c r="R7" s="9" t="n">
+        <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>13.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
+        <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>21.7</v>
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="W7" s="10" t="n">
-        <v>0.3</v>
+        <v>28.9</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>86.3</v>
+        <v>1.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>16.3</v>
+        <v>116.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>2.8</v>
+        <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1109,73 +1108,75 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>285.1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>24.4</v>
+        <v>485.1</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>34.4</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="9" t="n">
         <v>22.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>11.6</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M8" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>3262</v>
+        <v>36.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="9" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="T8" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="Y8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="n">
+        <v>45.3</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1190,15 +1191,17 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19656.5</v>
+        <v>2636.1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1169.7</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="F9" s="11" t="inlineStr"/>
+        <v>169.7</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1113.4</v>
+      </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
       </c>
@@ -1206,55 +1209,55 @@
         <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>14.2</v>
+        <v>44.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L9" s="9" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M9" s="9" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>167.1</v>
+      </c>
+      <c r="M9" s="10" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>121.7</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>169</v>
-      </c>
-      <c r="R9" s="9" t="n">
-        <v>71.8</v>
+        <v>165</v>
+      </c>
+      <c r="R9" s="10" t="n">
+        <v>171.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>27.7</v>
+        <v>127.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1224.1</v>
-      </c>
-      <c r="V9" s="9" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="V9" s="10" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="10" t="n">
         <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>8.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1186.2</v>
+        <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>120.2</v>
@@ -1275,20 +1278,20 @@
       <c r="C10" s="3" t="n">
         <v>531.2</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="E10" s="10" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>2.3</v>
+      <c r="H10" s="11" t="n">
+        <v>47.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1297,10 +1300,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="10" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1308,7 +1311,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>33</v>
@@ -1325,20 +1328,20 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>13.9</v>
+      <c r="W10" s="10" t="n">
+        <v>19.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>87.8</v>
+        <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
+        <v>1106.2</v>
+      </c>
+      <c r="Z10" s="3" t="n">
         <v>21.2</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1357,13 +1360,13 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>88.90000000000001</v>
+      <c r="F11" s="13" t="n">
+        <v>83.8</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.3</v>
@@ -1371,47 +1374,51 @@
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>16.5</v>
+      <c r="I11" s="11" t="n">
+        <v>46.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L11" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L11" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="W11" s="13" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>14</v>
+      </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1431,14 +1438,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="E12" s="13" t="inlineStr"/>
-      <c r="F12" s="8" t="n">
+      <c r="D12" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1450,53 +1457,53 @@
       <c r="J12" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3" t="n">
+      <c r="K12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>14.4</v>
+      <c r="P12" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16</v>
+        <v>6.5</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="11" t="n">
         <v>29.2</v>
       </c>
-      <c r="V12" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W12" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="X12" s="8" t="n">
-        <v>62.3</v>
+      <c r="V12" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X12" s="11" t="n">
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1417</v>
+        <v>47</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1517,8 +1524,8 @@
       <c r="D13" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>15.9</v>
+      <c r="E13" s="13" t="n">
+        <v>42.4</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>24.9</v>
@@ -1526,34 +1533,36 @@
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="11" t="n">
+        <v>11.4</v>
+      </c>
       <c r="I13" s="3" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>849</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.3</v>
+      <c r="R13" s="11" t="n">
+        <v>15.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1561,10 +1570,10 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>28.7</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1574,10 +1583,10 @@
         <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>0.2</v>
+        <v>28.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.5</v>
+        <v>25.4</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1593,13 +1602,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
@@ -1616,53 +1625,51 @@
       <c r="J14" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3" t="n">
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="10" t="n">
-        <v>4.5</v>
+      <c r="R14" s="11" t="n">
+        <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>73.8</v>
+        <v>7.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="V14" s="3" t="n">
+      <c r="U14" s="11" t="n">
+        <v>236</v>
+      </c>
+      <c r="V14" s="9" t="n">
         <v>27</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1020.8</v>
+        <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>231.2</v>
+        <v>114.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1678,18 +1685,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2652.1</v>
+        <v>552.9</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="G15" s="8" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1701,48 +1708,52 @@
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>148.8</v>
+        <v>418</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="13" t="inlineStr"/>
-      <c r="S15" s="8" t="n">
-        <v>0.8</v>
+      <c r="R15" s="11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
+        <v>115.4</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V15" s="10" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W15" s="8" t="n">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>23.4</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1757,74 +1768,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>257.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>8291.6</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>1118.2</v>
+        <v>237.7</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1291.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>2118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>61.8</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>97.3</v>
+        <v>397.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>56.2</v>
+        <v>136.2</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="9" t="n">
-        <v>22.1</v>
+      <c r="L16" s="10" t="n">
+        <v>880.9</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212.5</v>
+        <v>212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>184.7</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>83.59999999999999</v>
+        <v>154.7</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>173.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>128.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>131.3</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>22.8</v>
+      <c r="W16" s="10" t="n">
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>1145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1024.4</v>
+        <v>1224.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1840,43 +1853,43 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2313.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F17" s="9" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F17" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="10" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1884,22 +1897,22 @@
       <c r="Q17" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="10" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>27.4</v>
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>37.6</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>946.5</v>
-      </c>
-      <c r="W17" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W17" s="10" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1909,7 +1922,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>29.9</v>
+        <v>24.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1925,74 +1938,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+        <v>252.1</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>20.5</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>15.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>7.6</v>
+      <c r="L18" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>2.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>137.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="10" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="R18" s="12" t="n">
+      <c r="Q18" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R18" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.3</v>
+        <v>115.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V18" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>14.4</v>
+      <c r="W18" s="13" t="n">
+        <v>84.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>292.8</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2008,12 +2021,12 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.1</v>
+        <v>326.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="9" t="n">
         <v>12.3</v>
       </c>
       <c r="F19" s="3" t="n">
@@ -2025,24 +2038,26 @@
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+      <c r="I19" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>20.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="10" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="M19" s="12" t="n">
+      <c r="L19" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
@@ -2050,7 +2065,7 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="12" t="n">
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2062,20 +2077,20 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="10" t="n">
-        <v>96.90000000000001</v>
+      <c r="V19" s="11" t="n">
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>292.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2091,16 +2106,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>322.8</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>4.8</v>
+        <v>322.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>12.3</v>
+        <v>20.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2115,16 +2130,16 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L20" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>19.1</v>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2135,29 +2150,29 @@
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="12" t="n">
+      <c r="R20" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>44.8</v>
+        <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="11" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>118.2</v>
@@ -2181,17 +2196,17 @@
       <c r="D21" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>86.40000000000001</v>
+      <c r="E21" s="9" t="n">
+        <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2200,19 +2215,19 @@
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
@@ -2220,23 +2235,23 @@
       <c r="Q21" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="12" t="n">
+      <c r="R21" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>17.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="10" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="W21" s="10" t="n">
-        <v>0.4</v>
+      <c r="V21" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
@@ -2245,7 +2260,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>44.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2261,12 +2276,12 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>936.3</v>
+        <v>536.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="F22" s="3" t="n">
@@ -2281,50 +2296,48 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="M22" s="11" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="12" t="n">
+      <c r="R22" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="U22" s="8" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="U22" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2348,14 +2361,14 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="10" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>1117.1</v>
+      <c r="E23" s="10" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
@@ -2369,32 +2382,30 @@
       <c r="J23" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="10" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M23" s="12" t="n">
+      <c r="L23" s="10" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="M23" s="10" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1272</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q23" s="9" t="n">
-        <v>254.4</v>
-      </c>
-      <c r="R23" s="9" t="n">
-        <v>23.5</v>
-      </c>
+        <v>41.2</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>154.4</v>
+      </c>
+      <c r="R23" s="14" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>368.6</v>
+        <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2402,20 +2413,20 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>68.8</v>
+      <c r="V23" s="10" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2431,49 +2442,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>503.5</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>509.5</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>2.2</v>
+      <c r="H24" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>18.1</v>
+      <c r="J24" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>24.6</v>
+        <v>294.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R24" s="12" t="n">
+      <c r="Q24" s="10" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2485,11 +2498,11 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>1.6</v>
+      <c r="W24" s="10" t="n">
+        <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
@@ -2514,18 +2527,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
+        <v>45.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F25" s="12" t="n">
+      <c r="E25" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2537,53 +2550,53 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="9" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>401</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>14</v>
+        <v>40</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>14.8</v>
       </c>
       <c r="Q25" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="R25" s="12" t="n">
+      <c r="S25" s="11" t="n">
         <v>14.8</v>
       </c>
-      <c r="S25" s="8" t="n">
-        <v>37.3</v>
-      </c>
       <c r="T25" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V25" s="10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U25" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y25" s="3" t="n">
-        <v>41.6</v>
-      </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>457.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2604,16 +2617,16 @@
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>22.1</v>
+      <c r="F26" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="H26" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2625,10 +2638,10 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M26" s="8" t="n">
+      <c r="L26" s="9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M26" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2640,10 +2653,10 @@
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="10" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="R26" s="12" t="n">
+      <c r="Q26" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2652,23 +2665,23 @@
       <c r="T26" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="11" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W26" s="8" t="n">
+      <c r="V26" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W26" s="11" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.1</v>
+        <v>25</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2684,15 +2697,15 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="E27" s="3" t="n">
+        <v>550.1</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E27" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="11" t="n">
         <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2702,58 +2715,58 @@
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J27" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="12" t="n">
+      <c r="R27" s="11" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>7.1</v>
+        <v>1.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W27" s="10" t="n">
-        <v>0.1</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>196.5</v>
+        <v>26.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2769,75 +2782,77 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
+        <v>621</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="8" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="F28" s="12" t="n">
+      <c r="E28" s="9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="H28" s="8" t="n">
+      <c r="G28" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="P28" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="P28" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="10" t="n">
-        <v>80.39</v>
-      </c>
-      <c r="R28" s="12" t="n">
+      <c r="Q28" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
+        <v>598.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V28" s="9" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2852,16 +2867,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.8</v>
+        <v>624.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>23.3</v>
+      <c r="F29" s="11" t="n">
+        <v>38.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
@@ -2873,15 +2888,15 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="L29" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2893,10 +2908,10 @@
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q29" s="10" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="R29" s="12" t="n">
+      <c r="Q29" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R29" s="11" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2905,14 +2920,14 @@
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="11" t="n">
         <v>47.1</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>13.3</v>
+      <c r="W29" s="13" t="n">
+        <v>3.3</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>6.9</v>
@@ -2921,7 +2936,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>23009</v>
+        <v>30.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2937,58 +2952,58 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2281.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>1561.6</v>
+        <v>2781.9</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>161.6</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>714.5</v>
-      </c>
-      <c r="F30" s="9" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>237</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>118.9</v>
+        <v>135.8</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>18.9</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>91.7</v>
       </c>
-      <c r="Q30" s="9" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="R30" s="9" t="n">
-        <v>0.9</v>
+      <c r="Q30" s="10" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R30" s="10" t="n">
+        <v>20.9</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
@@ -2996,17 +3011,15 @@
       <c r="V30" s="9" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="9" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>110</v>
-      </c>
+      <c r="W30" s="10" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>106.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.8</v>
+        <v>122.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3022,15 +3035,15 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="9" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>32.3</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3042,17 +3055,15 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="11" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0.8</v>
@@ -3060,17 +3071,17 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P31" s="11" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="12" t="n">
+      <c r="R31" s="10" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3081,17 +3092,17 @@
       <c r="V31" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.2</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>24.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3107,23 +3118,21 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>61.1</v>
+        <v>208.6</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>23.8</v>
+        <v>33.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -3131,24 +3140,24 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>1.4</v>
+        <v>10</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>33.6</v>
       </c>
       <c r="R32" s="3" t="n">
@@ -3158,25 +3167,23 @@
         <v>14.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>19</v>
+        <v>1141.1</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>28.3</v>
+        <v>484.1</v>
+      </c>
+      <c r="V32" s="13" t="n">
+        <v>90.8</v>
       </c>
       <c r="W32" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>484.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
         <v>13.7</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3192,25 +3199,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>122.5</v>
+        <v>443.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="11" t="n">
         <v>14.3</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="11" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3218,14 +3225,14 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>41</v>
@@ -3233,10 +3240,10 @@
       <c r="P33" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3245,23 +3252,23 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="8" t="n">
-        <v>93.40000000000001</v>
+      <c r="U33" s="11" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X33" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="X33" s="11" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>149.2</v>
+        <v>1420.9</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>43.2</v>
+        <v>113.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3282,20 +3289,20 @@
       <c r="D34" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F34" s="12" t="n">
+      <c r="E34" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="11" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3306,11 +3313,11 @@
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="10" t="n">
-        <v>81.40000000000001</v>
+      <c r="M34" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>22.2</v>
@@ -3318,35 +3325,35 @@
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>19</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+        <v>12.7</v>
+      </c>
+      <c r="X34" s="11" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1801.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3362,31 +3369,31 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>439.9</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>50.3</v>
+        <v>433.9</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>30.3</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="11" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="11" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>14.3</v>
+        <v>47.1</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3395,7 +3402,7 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>1.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
@@ -3403,18 +3410,20 @@
       <c r="P35" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q35" s="13" t="inlineStr"/>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q35" s="9" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="R35" s="13" t="n">
+        <v>58.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>23.4</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3426,9 +3435,11 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>2121.5</v>
-      </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3445,24 +3456,28 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E36" s="13" t="inlineStr"/>
-      <c r="F36" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H36" s="8" t="n">
+      <c r="D36" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="13" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K36" s="12" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3473,40 +3488,40 @@
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>2.4</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="V36" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="V36" s="13" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>10.6</v>
+      <c r="X36" s="11" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1186</v>
+        <v>146.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3524,74 +3539,72 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>11810.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
+      <c r="D37" s="10" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>168.9</v>
       </c>
-      <c r="F37" s="9" t="n">
-        <v>110.2</v>
+      <c r="F37" s="10" t="n">
+        <v>110.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>33.8</v>
+        <v>55.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="M37" s="9" t="n">
-        <v>3.2</v>
+      <c r="M37" s="10" t="n">
+        <v>153.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.7</v>
+        <v>44.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1240.2</v>
+        <v>2409.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="R37" s="9" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="Q37" s="10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="R37" s="10" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1151</v>
+        <v>171.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="W37" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>49.8</v>
-      </c>
+      <c r="V37" s="10" t="n">
+        <v>1141.1</v>
+      </c>
+      <c r="W37" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>1181.2</v>
+        <v>188.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3607,66 +3620,64 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>442.2</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E38" s="9" t="n">
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>13.8</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
+      <c r="G38" s="11" t="n">
+        <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.2</v>
+        <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="10" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>27.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="9" t="n">
-        <v>14.8</v>
+      <c r="R38" s="10" t="n">
+        <v>14.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="10" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3692,40 +3703,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>914.6</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>18.66</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>811</v>
-      </c>
-      <c r="H39" s="8" t="n">
+        <v>5914.6</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.9</v>
+        <v>17.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M39" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M39" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>21</v>
@@ -3733,7 +3744,7 @@
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="12" t="n">
+      <c r="Q39" s="9" t="n">
         <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3743,25 +3754,25 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="U39" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="U39" s="11" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="12" t="n">
+      <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>28.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3777,76 +3788,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>641.4</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="E40" s="3" t="n">
+        <v>617.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.1</v>
+        <v>21.7</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="12" t="n">
+      <c r="Q40" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="V40" s="12" t="n">
-        <v>26</v>
+        <v>94.2</v>
+      </c>
+      <c r="V40" s="13" t="n">
+        <v>26.8</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="11" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.1</v>
+        <v>223.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3867,17 +3878,17 @@
       <c r="D41" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="E41" s="9" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="11" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>13</v>
+      <c r="H41" s="11" t="n">
+        <v>53</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3888,22 +3899,22 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="8" t="n">
-        <v>11.9</v>
+      <c r="M41" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P41" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="P41" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="12" t="n">
+      <c r="Q41" s="9" t="n">
         <v>29.8</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3913,23 +3924,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="12" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X41" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y41" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>128.9</v>
+      </c>
       <c r="Z41" s="3" t="n">
-        <v>0.2</v>
+        <v>26.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3948,16 +3961,16 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E42" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="G42" s="8" t="n">
-        <v>18.8</v>
+      <c r="G42" s="11" t="n">
+        <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>12</v>
@@ -3966,27 +3979,27 @@
         <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="L42" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q42" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q42" s="9" t="n">
         <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -3996,24 +4009,26 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.7</v>
+        <v>128.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>23</v>
+      <c r="V42" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>1392</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4028,22 +4043,22 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>534</v>
+        <v>234</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E43" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="G43" s="11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4052,24 +4067,24 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L43" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q43" s="12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q43" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4079,16 +4094,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="U43" s="3" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="U43" s="11" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="12" t="n">
+      <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4097,7 +4112,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>124.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4113,15 +4128,15 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="11" t="n">
         <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4137,51 +4152,53 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L44" s="12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L44" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="10" t="n">
-        <v>4.8</v>
+      <c r="M44" s="9" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="P44" s="3" t="n">
+        <v>644</v>
+      </c>
+      <c r="P44" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="12" t="n">
+      <c r="Q44" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="11" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V44" s="12" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="U44" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>0.1</v>
+      <c r="X44" s="11" t="n">
+        <v>227.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>290.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>112.4</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4196,72 +4213,70 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1801.1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>1122.1</v>
+        <v>2312.2</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>113.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>910.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>21.7</v>
+        <v>7194.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>721.1</v>
+        <v>85</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="9" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>1281.8</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>80.09999999999999</v>
+      <c r="K45" s="10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>1202.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>27.1</v>
+        <v>2.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>1226.5</v>
+        <v>226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>81.5</v>
-      </c>
+        <v>2908.4</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="R45" s="14" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>180</v>
+        <v>182.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="9" t="n">
-        <v>144.2</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>28.8</v>
+        <v>136.9</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>286.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>1222.9</v>
-      </c>
+        <v>164.7</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4277,76 +4292,74 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>561.8</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>40.6</v>
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>70.59999999999999</v>
       </c>
       <c r="E46" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>83</v>
+      <c r="F46" s="10" t="n">
+        <v>22.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L46" s="12" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>80.8</v>
+        <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="12" t="n">
+      <c r="Q46" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>9</v>
+      <c r="R46" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="S46" s="11" t="n">
+        <v>39</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="W46" s="9" t="n">
+      <c r="U46" s="11" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="V46" s="10" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W46" s="10" t="n">
         <v>12.4</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>112.6</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -47,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,25 +146,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,13 +777,13 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="E4" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="G4" s="3" t="n">
@@ -802,22 +793,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="9" t="n">
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>14.6</v>
+      <c r="M4" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -825,21 +816,21 @@
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>11.3</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="12" t="inlineStr"/>
-      <c r="W4" s="12" t="inlineStr"/>
+      <c r="V4" s="10" t="inlineStr"/>
+      <c r="W4" s="10" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -857,18 +848,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
-      </c>
-      <c r="D5" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -880,26 +871,26 @@
       <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="9" t="n">
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>15.5</v>
+      <c r="M5" s="8" t="n">
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -908,7 +899,7 @@
       <c r="T5" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="U5" s="11" t="n">
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
@@ -918,10 +909,10 @@
         <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>16.8</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -942,17 +933,17 @@
       <c r="C6" s="3" t="n">
         <v>504.8</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>33.9</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>23.9</v>
+      <c r="G6" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -963,26 +954,26 @@
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1007,7 +998,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1025,16 +1016,16 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>35.3</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1046,32 +1037,32 @@
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
@@ -1086,10 +1077,10 @@
         <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>33.4</v>
@@ -1110,13 +1101,13 @@
       <c r="C8" s="3" t="n">
         <v>485.1</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>34.4</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1128,16 +1119,16 @@
       <c r="I8" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1147,10 +1138,10 @@
       <c r="P8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1160,12 +1151,12 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.7</v>
+        <v>51.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1191,16 +1182,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636.1</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>2656</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>169.7</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1113.4</v>
+      <c r="E9" s="8" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>111.4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
@@ -1214,53 +1205,53 @@
       <c r="J9" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>167.1</v>
-      </c>
-      <c r="M9" s="10" t="n">
+      <c r="K9" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="Q9" s="9" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="Q9" s="8" t="n">
         <v>165</v>
       </c>
-      <c r="R9" s="10" t="n">
-        <v>171.8</v>
+      <c r="R9" s="8" t="n">
+        <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="V9" s="10" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="V9" s="11" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="10" t="n">
-        <v>169.6</v>
+      <c r="W9" s="11" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>120.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1278,20 +1269,20 @@
       <c r="C10" s="3" t="n">
         <v>531.2</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="D10" s="8" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="11" t="n">
-        <v>47.8</v>
+      <c r="H10" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1300,10 +1291,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1313,10 +1304,10 @@
       <c r="P10" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1328,17 +1319,17 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="11" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="10" t="n">
-        <v>19.9</v>
+      <c r="W10" s="11" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1106.2</v>
+        <v>106.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>21.2</v>
@@ -1357,16 +1348,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>30.8</v>
+        <v>27.9</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>30.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="13" t="n">
-        <v>83.8</v>
+      <c r="F11" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.3</v>
@@ -1374,23 +1365,23 @@
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>46.9</v>
+      <c r="I11" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L11" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L11" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1398,7 +1389,7 @@
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1410,14 +1401,14 @@
       <c r="T11" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="U11" s="11" t="n">
+      <c r="U11" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="11" t="n">
-        <v>14</v>
+      <c r="W11" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1438,14 +1429,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="11" t="n">
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1457,28 +1448,28 @@
       <c r="J12" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+      <c r="P12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R12" s="13" t="n">
+      <c r="R12" s="12" t="n">
         <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1487,17 +1478,17 @@
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="U12" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="W12" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" s="11" t="n">
-        <v>2.3</v>
+      <c r="W12" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>47</v>
@@ -1521,19 +1512,19 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="8" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>42.4</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1542,13 +1533,13 @@
       <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1558,11 +1549,11 @@
       <c r="P13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="11" t="n">
-        <v>15.8</v>
+      <c r="R13" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1570,13 +1561,13 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="V13" s="9" t="n">
+      <c r="U13" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1604,13 +1595,13 @@
       <c r="C14" s="3" t="n">
         <v>488</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="8" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1625,14 +1616,14 @@
       <c r="J14" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="11" t="n">
-        <v>22</v>
+      <c r="M14" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
@@ -1641,10 +1632,10 @@
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1653,23 +1644,23 @@
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="11" t="n">
-        <v>236</v>
-      </c>
-      <c r="V14" s="9" t="n">
+      <c r="U14" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>114.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1685,18 +1676,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.9</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>31.5</v>
+        <v>552.1</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>31.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1708,41 +1699,41 @@
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>418</v>
+        <v>48</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
+        <v>15.4</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1768,40 +1759,40 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.7</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>1291.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="E16" s="11" t="n">
         <v>76.8</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>2118.2</v>
+      <c r="F16" s="8" t="n">
+        <v>118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>397.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>136.2</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>880.9</v>
-      </c>
-      <c r="M16" s="10" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>212.5</v>
@@ -1809,35 +1800,35 @@
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>154.7</v>
       </c>
-      <c r="R16" s="10" t="n">
-        <v>173.6</v>
+      <c r="R16" s="11" t="n">
+        <v>73.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>188.2</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>131.3</v>
-      </c>
-      <c r="W16" s="10" t="n">
-        <v>12.8</v>
+      <c r="V16" s="8" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="W16" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1145.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1224.4</v>
+        <v>124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1853,25 +1844,25 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E17" s="10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>13.4</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
@@ -1879,14 +1870,14 @@
       <c r="K17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L17" s="9" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
@@ -1894,10 +1885,10 @@
       <c r="P17" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1909,14 +1900,14 @@
       <c r="U17" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>29.2</v>
@@ -1938,12 +1929,12 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>252.1</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="E18" s="9" t="n">
+        <v>552.1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="F18" s="3" t="n">
@@ -1959,26 +1950,26 @@
         <v>8</v>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>2.6</v>
+      <c r="L18" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>137.5</v>
+        <v>27.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="11" t="n">
-        <v>29.1</v>
+      <c r="Q18" s="8" t="n">
+        <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>15.2</v>
@@ -1987,16 +1978,16 @@
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
+        <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="13" t="n">
-        <v>84.40000000000001</v>
+      <c r="W18" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>8.4</v>
@@ -2005,7 +1996,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2021,12 +2012,12 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
+        <v>526.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="F19" s="3" t="n">
@@ -2041,28 +2032,28 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="K19" s="3" t="n">
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="8" t="n">
         <v>32</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2077,14 +2068,14 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2111,7 +2102,7 @@
       <c r="D20" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
@@ -2129,17 +2120,17 @@
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L20" s="11" t="n">
+      <c r="K20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2147,7 +2138,7 @@
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="8" t="n">
         <v>28.3</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2162,10 +2153,10 @@
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="11" t="n">
+      <c r="W20" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2175,7 +2166,7 @@
         <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>118.2</v>
+        <v>18.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2191,12 +2182,12 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>42.2</v>
+        <v>542.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
@@ -2206,7 +2197,7 @@
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2214,25 +2205,25 @@
       <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.7</v>
       </c>
       <c r="R21" s="3" t="n">
@@ -2242,15 +2233,15 @@
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2281,7 +2272,7 @@
       <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="F22" s="3" t="n">
@@ -2296,16 +2287,16 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2315,7 +2306,7 @@
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="8" t="n">
         <v>31.3</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2325,15 +2316,15 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W22" s="3" t="n">
+      <c r="V22" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2359,51 +2350,51 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2517.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>2547.5</v>
+      </c>
+      <c r="D23" s="11" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="11" t="n">
         <v>72.5</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="11" t="n">
         <v>117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="8" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="Q23" s="10" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>154.4</v>
       </c>
-      <c r="R23" s="14" t="inlineStr"/>
+      <c r="R23" s="13" t="inlineStr"/>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
@@ -2413,14 +2404,14 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="8" t="n">
         <v>130.5</v>
       </c>
-      <c r="W23" s="10" t="n">
-        <v>168.8</v>
+      <c r="W23" s="8" t="n">
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
@@ -2444,13 +2435,13 @@
       <c r="C24" s="3" t="n">
         <v>509.5</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2468,22 +2459,22 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M24" s="10" t="n">
+      <c r="L24" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M24" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>294.6</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="R24" s="3" t="n">
@@ -2498,20 +2489,20 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="10" t="n">
+      <c r="V24" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2527,18 +2518,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2550,13 +2541,13 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2565,38 +2556,38 @@
       <c r="O25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="P25" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>11.4</v>
+      <c r="P25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="12" t="n">
+        <v>1.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="S25" s="11" t="n">
+      <c r="S25" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="U25" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V25" s="9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V25" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>457.3</v>
+        <v>45.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2614,20 +2605,20 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>22</v>
+      <c r="F26" s="8" t="n">
+        <v>22.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.8</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>7.3</v>
@@ -2635,20 +2626,20 @@
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2660,25 +2651,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="U26" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W26" s="11" t="n">
+      <c r="W26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>25</v>
@@ -2699,13 +2690,13 @@
       <c r="C27" s="3" t="n">
         <v>550.1</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2715,18 +2706,18 @@
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2741,29 +2732,29 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>27.2</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>26.6</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>26.3</v>
@@ -2784,43 +2775,43 @@
       <c r="C28" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>18.1</v>
+      <c r="G28" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K28" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P28" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
@@ -2830,15 +2821,15 @@
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>598.4</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="V28" s="9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2869,14 +2860,14 @@
       <c r="C29" s="3" t="n">
         <v>624.9</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="8" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>38.3</v>
+      <c r="F29" s="8" t="n">
+        <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
@@ -2890,13 +2881,13 @@
       <c r="J29" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2911,22 +2902,22 @@
       <c r="Q29" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U29" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>47.1</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="13" t="n">
+      <c r="W29" s="12" t="n">
         <v>3.3</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2936,7 +2927,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2954,13 +2945,13 @@
       <c r="C30" s="3" t="n">
         <v>2781.9</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="8" t="n">
         <v>161.6</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="11" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2970,19 +2961,19 @@
         <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L30" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L30" s="8" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="10" t="n">
-        <v>30.6</v>
+      <c r="M30" s="8" t="n">
+        <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.3</v>
@@ -2991,27 +2982,27 @@
         <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="Q30" s="10" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="R30" s="10" t="n">
-        <v>20.9</v>
+        <v>51.7</v>
+      </c>
+      <c r="Q30" s="11" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>22.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="11" t="n">
         <v>66.8</v>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -3035,15 +3026,15 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>336.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="D31" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3055,14 +3046,14 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3071,17 +3062,17 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="11" t="n">
+      <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3089,17 +3080,17 @@
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="11" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>21.6</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>1.8</v>
@@ -3118,7 +3109,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>208.6</v>
+        <v>611.1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
@@ -3126,7 +3117,7 @@
       <c r="E32" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3140,16 +3131,16 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>5.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
@@ -3157,23 +3148,23 @@
       <c r="P32" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1141.1</v>
+        <v>15.1</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
       </c>
-      <c r="V32" s="13" t="n">
-        <v>90.8</v>
+      <c r="V32" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>28.5</v>
@@ -3199,25 +3190,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>443.7</v>
+        <v>43.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F33" s="9" t="n">
+      <c r="E33" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3225,10 +3216,10 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3240,10 +3231,10 @@
       <c r="P33" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="11" t="n">
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3252,23 +3243,23 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="11" t="n">
-        <v>83.40000000000001</v>
+      <c r="U33" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="X33" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3292,17 +3283,17 @@
       <c r="E34" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3310,50 +3301,50 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>22.2</v>
+        <v>52.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25.9</v>
+        <v>15</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="11" t="n">
-        <v>11.8</v>
+      <c r="X34" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3377,47 +3368,47 @@
       <c r="E35" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="11" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>47.1</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R35" s="13" t="n">
-        <v>58.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
@@ -3432,7 +3423,7 @@
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0.2</v>
@@ -3456,17 +3447,17 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="12" t="n">
         <v>45.4</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>4.8</v>
+      <c r="G36" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
@@ -3477,26 +3468,26 @@
       <c r="J36" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K36" s="12" t="inlineStr"/>
-      <c r="L36" s="3" t="n">
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3506,22 +3497,22 @@
         <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="V36" s="13" t="n">
-        <v>82.09999999999999</v>
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="11" t="n">
-        <v>80.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>146.6</v>
+        <v>40</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>16.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3539,13 +3530,13 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>168.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
+      <c r="D37" s="11" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>110.3</v>
       </c>
       <c r="G37" s="3" t="n">
@@ -3560,51 +3551,51 @@
       <c r="J37" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K37" s="10" t="n">
+      <c r="K37" s="11" t="n">
         <v>36.1</v>
       </c>
-      <c r="L37" s="10" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>153.2</v>
+      <c r="L37" s="8" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>53.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>44.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>2409.2</v>
+        <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="R37" s="10" t="n">
-        <v>82.59999999999999</v>
+        <v>59.3</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="R37" s="8" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>171.6</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="10" t="n">
-        <v>1141.1</v>
-      </c>
-      <c r="W37" s="10" t="n">
-        <v>97</v>
+      <c r="V37" s="11" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="W37" s="11" t="n">
+        <v>7</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>188.2</v>
+        <v>187.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3622,62 +3613,62 @@
       <c r="C38" s="3" t="n">
         <v>443.3</v>
       </c>
-      <c r="D38" s="10" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="10" t="n">
+      <c r="D38" s="11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="10" t="n">
+      <c r="R38" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U38" s="11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="10" t="n">
+      <c r="V38" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="11" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3703,40 +3694,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5914.6</v>
+        <v>514.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="11" t="n">
+      <c r="H39" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>21</v>
@@ -3744,7 +3735,7 @@
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3754,12 +3745,12 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U39" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="U39" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3788,21 +3779,21 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
+        <v>17.1</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3814,22 +3805,22 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>21.7</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>30</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3842,22 +3833,22 @@
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V40" s="13" t="n">
-        <v>26.8</v>
+        <v>34.2</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="11" t="n">
+      <c r="X40" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>318</v>
+        <v>30</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>223.6</v>
+        <v>23.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3878,17 +3869,17 @@
       <c r="D41" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="11" t="n">
-        <v>53</v>
+      <c r="H41" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3899,22 +3890,22 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>11.1</v>
+      <c r="M41" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P41" s="11" t="n">
+      <c r="P41" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>29.8</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3926,20 +3917,20 @@
       <c r="T41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="U41" s="11" t="n">
+      <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.9</v>
+        <v>28.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>26.4</v>
@@ -3961,15 +3952,15 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="E42" s="9" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3984,10 +3975,10 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3999,7 +3990,7 @@
       <c r="P42" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4009,25 +4000,25 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>128.7</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="8" t="n">
         <v>19</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1392</v>
+        <v>52</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4043,21 +4034,21 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>234</v>
+        <v>554</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>30.5</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4067,24 +4058,24 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L43" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L43" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>31.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q43" s="9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4094,16 +4085,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="U43" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4133,10 +4124,10 @@
       <c r="D44" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="E44" s="9" t="n">
+      <c r="E44" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4152,52 +4143,52 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L44" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L44" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="9" t="n">
+      <c r="M44" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>644</v>
-      </c>
-      <c r="P44" s="11" t="n">
+        <v>244</v>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="9" t="n">
+      <c r="Q44" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>87.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="U44" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="11" t="n">
-        <v>227.9</v>
+      <c r="X44" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>290.8</v>
+        <v>50.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>112.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4213,68 +4204,68 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2312.2</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="E45" s="10" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="E45" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>113.8</v>
+      <c r="F45" s="11" t="n">
+        <v>13.8</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>910.8</v>
+        <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>7194.9</v>
+        <v>21.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="10" t="n">
+      <c r="K45" s="11" t="n">
         <v>12.2</v>
       </c>
-      <c r="L45" s="10" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="M45" s="10" t="n">
-        <v>1202.9</v>
+      <c r="L45" s="11" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>222.1</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>296.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2908.4</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>178</v>
-      </c>
-      <c r="R45" s="14" t="inlineStr"/>
+        <v>58.4</v>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="R45" s="13" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>182.8</v>
+        <v>23.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>136.9</v>
+        <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>182.6</v>
       </c>
-      <c r="V45" s="10" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>286.2</v>
+      <c r="V45" s="8" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="W45" s="11" t="n">
+        <v>22.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>164.7</v>
+        <v>54.7</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4294,72 +4285,74 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>22.3</v>
+      <c r="F46" s="11" t="n">
+        <v>2.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="9" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S46" s="11" t="n">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="11" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="10" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="X46" s="11" t="n">
-        <v>16.8</v>
+      <c r="U46" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W46" s="11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -149,16 +149,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -808,7 +808,7 @@
         <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -829,8 +829,8 @@
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="10" t="inlineStr"/>
+      <c r="V4" s="11" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>12.7</v>
+        <v>512.7</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>32.6</v>
@@ -897,7 +897,7 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>46.8</v>
@@ -1047,10 +1047,10 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
@@ -1151,7 +1151,7 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>51.7</v>
+        <v>31.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
@@ -1187,8 +1187,8 @@
       <c r="D9" s="8" t="n">
         <v>169.7</v>
       </c>
-      <c r="E9" s="8" t="n">
-        <v>53.3</v>
+      <c r="E9" s="9" t="n">
+        <v>33.3</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>111.4</v>
@@ -1238,10 +1238,10 @@
       <c r="U9" s="3" t="n">
         <v>224.1</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="9" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1319,10 +1319,10 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>27.9</v>
+        <v>427.9</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
@@ -1381,7 +1381,7 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>12.7</v>
+        <v>1.8</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1432,7 +1432,7 @@
       <c r="D12" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E12" s="10" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>21.7</v>
       </c>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>31.8</v>
@@ -1703,14 +1703,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>48</v>
+        <v>26.2</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1761,11 +1761,11 @@
       <c r="C16" s="3" t="n">
         <v>257.7</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="9" t="n">
         <v>159.6</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>76.8</v>
+      <c r="E16" s="9" t="n">
+        <v>26.8</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>118.2</v>
@@ -1780,22 +1780,22 @@
         <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>56.2</v>
+        <v>36.2</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="L16" s="9" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="M16" s="8" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>218.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
@@ -1803,7 +1803,7 @@
       <c r="Q16" s="8" t="n">
         <v>154.7</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="9" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1816,10 +1816,10 @@
         <v>188.2</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="W16" s="11" t="n">
-        <v>72.5</v>
+        <v>131.3</v>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>12.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
@@ -1844,19 +1844,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>15.4</v>
+        <v>515.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1888,7 +1888,7 @@
       <c r="Q17" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>552.1</v>
+        <v>352.1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.9</v>
@@ -1937,7 +1937,7 @@
       <c r="E18" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1960,10 +1960,10 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
@@ -1981,7 +1981,7 @@
         <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>22.2</v>
+        <v>40.4</v>
       </c>
       <c r="V18" s="8" t="n">
         <v>28.1</v>
@@ -2020,7 +2020,7 @@
       <c r="E19" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2075,7 +2075,7 @@
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2105,8 +2105,8 @@
       <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>20.3</v>
+      <c r="F20" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2190,7 +2190,7 @@
       <c r="E21" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2275,7 +2275,7 @@
       <c r="E22" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2300,7 +2300,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
@@ -2352,26 +2352,26 @@
       <c r="C23" s="3" t="n">
         <v>2547.5</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="9" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="E23" s="8" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>61</v>
+        <v>22.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>3.3</v>
@@ -2383,7 +2383,7 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>273</v>
@@ -2435,13 +2435,13 @@
       <c r="C24" s="3" t="n">
         <v>509.5</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="9" t="n">
         <v>32.1</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2560,7 +2560,7 @@
         <v>14</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
@@ -2612,10 +2612,10 @@
         <v>14.8</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>11.6</v>
@@ -2636,7 +2636,7 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>22</v>
@@ -2721,10 +2721,10 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>9.9</v>
@@ -2824,10 +2824,10 @@
         <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
+        <v>19.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>43.4</v>
+        <v>13.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
@@ -2870,7 +2870,7 @@
         <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
@@ -2891,7 +2891,7 @@
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>41.3</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
+        <v>271.9</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>161.6</v>
@@ -2951,7 +2951,7 @@
       <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="9" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2964,7 +2964,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>25.8</v>
+        <v>35.8</v>
       </c>
       <c r="K30" s="8" t="n">
         <v>10.9</v>
@@ -2984,14 +2984,14 @@
       <c r="P30" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="Q30" s="11" t="n">
+      <c r="Q30" s="9" t="n">
         <v>155.1</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="9" t="n">
         <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>72.59999999999999</v>
@@ -3002,7 +3002,7 @@
       <c r="V30" s="8" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="11" t="n">
+      <c r="W30" s="9" t="n">
         <v>66.8</v>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
@@ -3065,14 +3065,14 @@
       <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="11" t="n">
+      <c r="Q31" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3083,17 +3083,17 @@
       <c r="V31" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="11" t="n">
+      <c r="W31" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>21.6</v>
+        <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>15.1</v>
+        <v>1.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>43.7</v>
+        <v>243.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
@@ -3244,7 +3244,7 @@
         <v>30.3</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>23.4</v>
+        <v>13.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
@@ -3293,7 +3293,7 @@
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3308,10 +3308,10 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>52.2</v>
+        <v>32.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3341,10 +3341,10 @@
         <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>9.6</v>
@@ -3454,7 +3454,7 @@
         <v>11.2</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>14.3</v>
@@ -3468,7 +3468,7 @@
       <c r="J36" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K36" s="10" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="8" t="n">
         <v>17.8</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>40</v>
+        <v>20.2</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>16.6</v>
@@ -3530,20 +3530,20 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="9" t="n">
         <v>151.6</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="9" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="8" t="n">
         <v>110.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>55.8</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3551,7 +3551,7 @@
       <c r="J37" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="9" t="n">
         <v>36.1</v>
       </c>
       <c r="L37" s="8" t="n">
@@ -3567,7 +3567,7 @@
         <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.3</v>
+        <v>39.3</v>
       </c>
       <c r="Q37" s="8" t="n">
         <v>133.5</v>
@@ -3584,11 +3584,11 @@
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="11" t="n">
+      <c r="V37" s="9" t="n">
         <v>114.1</v>
       </c>
-      <c r="W37" s="11" t="n">
-        <v>7</v>
+      <c r="W37" s="9" t="n">
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
@@ -3613,10 +3613,10 @@
       <c r="C38" s="3" t="n">
         <v>443.3</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>13.8</v>
       </c>
       <c r="F38" s="8" t="n">
@@ -3634,7 +3634,9 @@
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
@@ -3642,7 +3644,7 @@
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
@@ -3660,15 +3662,15 @@
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>10.3</v>
+        <v>30.3</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="11" t="n">
+      <c r="W38" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3696,7 +3698,7 @@
       <c r="C39" s="3" t="n">
         <v>514.6</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="8" t="n">
         <v>29.2</v>
       </c>
       <c r="E39" s="8" t="n">
@@ -3730,7 +3732,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3779,9 +3781,9 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
+        <v>617.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
         <v>30.7</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -3812,7 +3814,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>51</v>
@@ -3866,7 +3868,7 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="E41" s="8" t="n">
@@ -3897,7 +3899,7 @@
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
@@ -3951,7 +3953,7 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="8" t="n">
         <v>31.2</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -4008,11 +4010,11 @@
       <c r="V42" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>23</v>
+      <c r="W42" s="12" t="n">
+        <v>12.3</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>52</v>
@@ -4036,7 +4038,7 @@
       <c r="C43" s="3" t="n">
         <v>554</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="8" t="n">
         <v>30.5</v>
       </c>
       <c r="E43" s="8" t="n">
@@ -4058,7 +4060,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>17.7</v>
@@ -4094,7 +4096,7 @@
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4121,7 +4123,7 @@
       <c r="C44" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="8" t="n">
         <v>30.7</v>
       </c>
       <c r="E44" s="8" t="n">
@@ -4143,7 +4145,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>16.6</v>
@@ -4152,10 +4154,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>10.6</v>
@@ -4170,7 +4172,7 @@
         <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>32.8</v>
@@ -4204,16 +4206,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>312.2</v>
-      </c>
-      <c r="D45" s="11" t="n">
+        <v>3312.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>185.7</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="F45" s="11" t="n">
-        <v>13.8</v>
+      <c r="F45" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>91.8</v>
@@ -4225,19 +4227,19 @@
         <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K45" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="L45" s="11" t="n">
+      <c r="L45" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="M45" s="11" t="n">
-        <v>222.1</v>
+      <c r="M45" s="9" t="n">
+        <v>224</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>2.7</v>
+        <v>27</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>296.5</v>
@@ -4261,11 +4263,11 @@
       <c r="V45" s="8" t="n">
         <v>144.2</v>
       </c>
-      <c r="W45" s="11" t="n">
-        <v>22.8</v>
+      <c r="W45" s="9" t="n">
+        <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>54.7</v>
+        <v>186.2</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4285,17 +4287,17 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>20.6</v>
+      <c r="D46" s="8" t="n">
+        <v>30.6</v>
       </c>
       <c r="E46" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
@@ -4316,7 +4318,7 @@
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>9.6</v>
+        <v>2.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>49.4</v>
@@ -4342,14 +4344,14 @@
       <c r="V46" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W46" s="11" t="n">
-        <v>14.4</v>
+      <c r="W46" s="9" t="n">
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>27.1</v>
+        <v>31.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>19.6</v>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -808,7 +808,7 @@
         <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -897,7 +897,7 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>46.8</v>
@@ -1047,10 +1047,10 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>36.2</v>
+        <v>26.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1151,7 +1151,7 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>31.7</v>
+        <v>51.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
@@ -1323,7 +1323,7 @@
         <v>27.9</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>13.9</v>
+        <v>19.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
@@ -1351,7 +1351,7 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
@@ -1381,7 +1381,7 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.7</v>
+        <v>0</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>31.1</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>49.5</v>
+        <v>149.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
@@ -1703,14 +1703,14 @@
         <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>26.2</v>
+        <v>48</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1765,7 +1765,7 @@
         <v>159.6</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>26.8</v>
+        <v>76.8</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>118.2</v>
@@ -1780,12 +1780,12 @@
         <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
+        <v>56.2</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="8" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="M16" s="8" t="n">
@@ -1819,7 +1819,7 @@
         <v>131.3</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>12.5</v>
+        <v>72.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>515.4</v>
+        <v>55.4</v>
       </c>
       <c r="D17" s="8" t="n">
         <v>31.9</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>23.6</v>
@@ -1868,7 +1868,7 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>18</v>
@@ -1877,7 +1877,7 @@
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>352.1</v>
+        <v>552.1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.9</v>
@@ -1937,7 +1937,7 @@
       <c r="E18" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1960,10 +1960,10 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>37.5</v>
+        <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
@@ -2020,7 +2020,7 @@
       <c r="E19" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="G19" s="3" t="n">
@@ -2075,7 +2075,7 @@
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2105,8 +2105,8 @@
       <c r="E20" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>24.3</v>
+      <c r="F20" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2190,7 +2190,7 @@
       <c r="E21" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2275,7 +2275,7 @@
       <c r="E22" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2300,7 +2300,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
@@ -2355,8 +2355,8 @@
       <c r="D23" s="9" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <v>73.5</v>
+      <c r="E23" s="9" t="n">
+        <v>78.5</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>117.1</v>
@@ -2365,13 +2365,13 @@
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>22.2</v>
+        <v>69</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>27.2</v>
+        <v>57.2</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>3.3</v>
@@ -2383,10 +2383,10 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>41.3</v>
@@ -2441,7 +2441,7 @@
       <c r="E24" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="G24" s="3" t="n">
@@ -2551,7 +2551,7 @@
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.9</v>
+        <v>9.9</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>40</v>
@@ -2560,7 +2560,7 @@
         <v>14</v>
       </c>
       <c r="Q25" s="12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
@@ -2612,10 +2612,10 @@
         <v>14.8</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>11.6</v>
@@ -2636,10 +2636,10 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2721,10 +2721,10 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>9.9</v>
@@ -2788,7 +2788,7 @@
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>20.4</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2824,10 +2824,10 @@
         <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>13.4</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>27.7</v>
@@ -2891,7 +2891,7 @@
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>41.3</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>271.9</v>
+        <v>2781.9</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>161.6</v>
@@ -2951,7 +2951,7 @@
       <c r="E30" s="8" t="n">
         <v>74.5</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>118</v>
       </c>
       <c r="G30" s="3" t="n">
@@ -2964,7 +2964,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="8" t="n">
         <v>10.9</v>
@@ -2997,7 +2997,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>19.4</v>
       </c>
       <c r="V30" s="8" t="n">
         <v>126.7</v>
@@ -3057,7 +3057,7 @@
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
@@ -3072,7 +3072,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3093,7 +3093,7 @@
         <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>611.1</v>
+        <v>61.1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
@@ -3140,7 +3140,7 @@
         <v>5.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
@@ -3158,7 +3158,7 @@
         <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>243.7</v>
+        <v>43.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
@@ -3244,7 +3244,7 @@
         <v>30.3</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>13.4</v>
+        <v>123.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
@@ -3256,7 +3256,7 @@
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>22.2</v>
+        <v>42.2</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>13.9</v>
@@ -3308,7 +3308,7 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>32.2</v>
@@ -3344,7 +3344,7 @@
         <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0.2</v>
+        <v>33.2</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>19.2</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>341.3</v>
+        <v>34.1</v>
       </c>
       <c r="D36" s="12" t="n">
         <v>45.4</v>
@@ -3509,7 +3509,7 @@
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>20.2</v>
+        <v>40</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>16.6</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2216.6</v>
+        <v>221.6</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>151.6</v>
@@ -3543,7 +3543,7 @@
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3588,7 +3588,7 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
@@ -3634,9 +3634,7 @@
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>16.8</v>
       </c>
@@ -3644,7 +3642,7 @@
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
@@ -3708,7 +3706,7 @@
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>11.2</v>
@@ -3729,7 +3727,7 @@
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>31</v>
@@ -3814,7 +3812,7 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>51</v>
@@ -3832,7 +3830,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>34.2</v>
@@ -3899,7 +3897,7 @@
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
@@ -3929,7 +3927,7 @@
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>28.4</v>
@@ -4011,10 +4009,10 @@
         <v>19</v>
       </c>
       <c r="W42" s="12" t="n">
-        <v>12.3</v>
+        <v>81.3</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>52</v>
@@ -4069,7 +4067,7 @@
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>31.5</v>
@@ -4121,7 +4119,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
+        <v>58</v>
       </c>
       <c r="D44" s="8" t="n">
         <v>30.7</v>
@@ -4154,7 +4152,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>18.1</v>
+        <v>0.8</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>44</v>
@@ -4172,7 +4170,7 @@
         <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>32.8</v>
@@ -4184,7 +4182,7 @@
         <v>14.7</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>12.9</v>
+        <v>10.9</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>50.8</v>
@@ -4206,7 +4204,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3312.2</v>
+        <v>331.2</v>
       </c>
       <c r="D45" s="9" t="n">
         <v>185.7</v>
@@ -4221,13 +4219,13 @@
         <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>32.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>12.2</v>
@@ -4235,11 +4233,11 @@
       <c r="L45" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="M45" s="9" t="n">
-        <v>224</v>
+      <c r="M45" s="8" t="n">
+        <v>65</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>27</v>
+        <v>57.8</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>296.5</v>
@@ -4258,7 +4256,7 @@
         <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>182.6</v>
+        <v>185.6</v>
       </c>
       <c r="V45" s="8" t="n">
         <v>144.2</v>
@@ -4267,7 +4265,7 @@
         <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>186.2</v>
+        <v>64.7</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4309,7 +4307,7 @@
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>16.8</v>
@@ -4318,7 +4316,7 @@
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>49.4</v>
@@ -4345,13 +4343,13 @@
         <v>24</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>31.1</v>
+        <v>21.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>19.6</v>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -1209,7 +1209,7 @@
       <c r="J9" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1373,7 +1373,7 @@
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="13" t="n"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="J16" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2370,7 +2370,7 @@
       <c r="J23" s="3" t="n">
         <v>57.2</v>
       </c>
-      <c r="K23" s="3" t="n"/>
+      <c r="K23" s="10" t="n"/>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>16.1</v>
       </c>
       <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
+      <c r="K25" s="13" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
@@ -2695,7 +2695,7 @@
       <c r="J27" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="13" t="n"/>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="J30" s="3" t="n">
         <v>35.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>81.8</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3527,7 +3527,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="10" t="n"/>
       <c r="L37" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
@@ -3693,7 +3693,7 @@
       <c r="J39" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="K39" s="3" t="n"/>
+      <c r="K39" s="13" t="n"/>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -4199,7 +4199,7 @@
       <c r="J45" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
